--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-06_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-06_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>9 October 2026</t>
+          <t>10 October 2026</t>
         </is>
       </c>
     </row>
@@ -1529,37 +1529,37 @@
         <v>167</v>
       </c>
       <c r="C5" s="12" t="n">
-        <v>39</v>
+        <v>167</v>
       </c>
       <c r="D5" s="12" t="n">
-        <v>110</v>
+        <v>0</v>
       </c>
       <c r="E5" s="12" t="n">
-        <v>18</v>
+        <v>0</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>23.4</v>
+        <v>100</v>
       </c>
       <c r="G5" s="12" t="n">
-        <v>89.2</v>
+        <v>100</v>
       </c>
       <c r="H5" s="12" t="n">
         <v>312</v>
       </c>
       <c r="I5" s="12" t="n">
-        <v>82</v>
+        <v>312</v>
       </c>
       <c r="J5" s="12" t="n">
-        <v>206</v>
+        <v>0</v>
       </c>
       <c r="K5" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="L5" s="12" t="n">
-        <v>26.3</v>
+        <v>100</v>
       </c>
       <c r="M5" s="12" t="n">
-        <v>92.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -1572,16 +1572,16 @@
         <v>5</v>
       </c>
       <c r="C6" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D6" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F6" s="12" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="G6" s="12" t="n">
         <v>100</v>
@@ -1590,16 +1590,16 @@
         <v>13</v>
       </c>
       <c r="I6" s="12" t="n">
-        <v>6</v>
+        <v>13</v>
       </c>
       <c r="J6" s="12" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="K6" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L6" s="12" t="n">
-        <v>46.2</v>
+        <v>100</v>
       </c>
       <c r="M6" s="12" t="n">
         <v>100</v>
@@ -1615,37 +1615,37 @@
         <v>15</v>
       </c>
       <c r="C7" s="12" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="D7" s="12" t="n">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="E7" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F7" s="12" t="n">
-        <v>13.3</v>
+        <v>100</v>
       </c>
       <c r="G7" s="12" t="n">
-        <v>80</v>
+        <v>100</v>
       </c>
       <c r="H7" s="12" t="n">
         <v>34</v>
       </c>
       <c r="I7" s="12" t="n">
-        <v>5</v>
+        <v>34</v>
       </c>
       <c r="J7" s="12" t="n">
-        <v>24</v>
+        <v>0</v>
       </c>
       <c r="K7" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L7" s="12" t="n">
-        <v>14.7</v>
+        <v>100</v>
       </c>
       <c r="M7" s="12" t="n">
-        <v>85.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="8">
@@ -1658,16 +1658,16 @@
         <v>11</v>
       </c>
       <c r="C8" s="12" t="n">
-        <v>2</v>
+        <v>11</v>
       </c>
       <c r="D8" s="12" t="n">
-        <v>9</v>
+        <v>0</v>
       </c>
       <c r="E8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F8" s="12" t="n">
-        <v>18.2</v>
+        <v>100</v>
       </c>
       <c r="G8" s="12" t="n">
         <v>100</v>
@@ -1676,16 +1676,16 @@
         <v>17</v>
       </c>
       <c r="I8" s="12" t="n">
-        <v>3</v>
+        <v>17</v>
       </c>
       <c r="J8" s="12" t="n">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="K8" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L8" s="12" t="n">
-        <v>17.6</v>
+        <v>100</v>
       </c>
       <c r="M8" s="12" t="n">
         <v>100</v>
@@ -1701,16 +1701,16 @@
         <v>7</v>
       </c>
       <c r="C9" s="12" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="D9" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F9" s="12" t="n">
-        <v>57.1</v>
+        <v>100</v>
       </c>
       <c r="G9" s="12" t="n">
         <v>100</v>
@@ -1719,16 +1719,16 @@
         <v>18</v>
       </c>
       <c r="I9" s="12" t="n">
-        <v>10</v>
+        <v>18</v>
       </c>
       <c r="J9" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K9" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L9" s="12" t="n">
-        <v>55.6</v>
+        <v>100</v>
       </c>
       <c r="M9" s="12" t="n">
         <v>100</v>
@@ -1744,16 +1744,16 @@
         <v>1</v>
       </c>
       <c r="C10" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D10" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="E10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F10" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G10" s="12" t="n">
         <v>100</v>
@@ -1762,16 +1762,16 @@
         <v>3</v>
       </c>
       <c r="I10" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J10" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J10" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K10" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L10" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M10" s="12" t="n">
         <v>100</v>
@@ -1787,16 +1787,16 @@
         <v>1</v>
       </c>
       <c r="C11" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D11" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D11" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="E11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F11" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G11" s="12" t="n">
         <v>100</v>
@@ -1805,16 +1805,16 @@
         <v>3</v>
       </c>
       <c r="I11" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J11" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J11" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K11" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L11" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M11" s="12" t="n">
         <v>100</v>
@@ -1830,16 +1830,16 @@
         <v>2</v>
       </c>
       <c r="C12" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D12" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F12" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G12" s="12" t="n">
         <v>100</v>
@@ -1848,16 +1848,16 @@
         <v>7</v>
       </c>
       <c r="I12" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J12" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K12" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L12" s="12" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="M12" s="12" t="n">
         <v>100</v>
@@ -1873,16 +1873,16 @@
         <v>1</v>
       </c>
       <c r="C13" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D13" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D13" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="E13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F13" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G13" s="12" t="n">
         <v>100</v>
@@ -1891,16 +1891,16 @@
         <v>4</v>
       </c>
       <c r="I13" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J13" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J13" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="K13" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L13" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M13" s="12" t="n">
         <v>100</v>
@@ -1916,16 +1916,16 @@
         <v>1</v>
       </c>
       <c r="C14" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D14" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D14" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="E14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F14" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G14" s="12" t="n">
         <v>100</v>
@@ -1934,16 +1934,16 @@
         <v>3</v>
       </c>
       <c r="I14" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J14" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J14" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K14" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L14" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M14" s="12" t="n">
         <v>100</v>
@@ -1959,37 +1959,37 @@
         <v>2</v>
       </c>
       <c r="C15" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E15" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F15" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G15" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H15" s="12" t="n">
         <v>5</v>
       </c>
       <c r="I15" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="J15" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K15" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L15" s="12" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="M15" s="12" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
     </row>
     <row r="16">
@@ -2002,37 +2002,37 @@
         <v>7</v>
       </c>
       <c r="C16" s="12" t="n">
+        <v>7</v>
+      </c>
+      <c r="D16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D16" s="12" t="n">
-        <v>6</v>
-      </c>
       <c r="E16" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F16" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G16" s="12" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H16" s="12" t="n">
         <v>12</v>
       </c>
       <c r="I16" s="12" t="n">
+        <v>12</v>
+      </c>
+      <c r="J16" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J16" s="12" t="n">
-        <v>11</v>
-      </c>
       <c r="K16" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L16" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M16" s="12" t="n">
-        <v>91.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="17">
@@ -2045,37 +2045,37 @@
         <v>11</v>
       </c>
       <c r="C17" s="12" t="n">
+        <v>11</v>
+      </c>
+      <c r="D17" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D17" s="12" t="n">
-        <v>7</v>
-      </c>
       <c r="E17" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F17" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G17" s="12" t="n">
-        <v>63.6</v>
+        <v>100</v>
       </c>
       <c r="H17" s="12" t="n">
         <v>15</v>
       </c>
       <c r="I17" s="12" t="n">
+        <v>15</v>
+      </c>
+      <c r="J17" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J17" s="12" t="n">
-        <v>10</v>
-      </c>
       <c r="K17" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="L17" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M17" s="12" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="18">
@@ -2088,16 +2088,16 @@
         <v>3</v>
       </c>
       <c r="C18" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D18" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F18" s="12" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="G18" s="12" t="n">
         <v>100</v>
@@ -2106,16 +2106,16 @@
         <v>7</v>
       </c>
       <c r="I18" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="J18" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K18" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L18" s="12" t="n">
-        <v>28.6</v>
+        <v>100</v>
       </c>
       <c r="M18" s="12" t="n">
         <v>100</v>
@@ -2131,16 +2131,16 @@
         <v>7</v>
       </c>
       <c r="C19" s="12" t="n">
-        <v>2</v>
+        <v>7</v>
       </c>
       <c r="D19" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F19" s="12" t="n">
-        <v>28.6</v>
+        <v>100</v>
       </c>
       <c r="G19" s="12" t="n">
         <v>100</v>
@@ -2149,16 +2149,16 @@
         <v>16</v>
       </c>
       <c r="I19" s="12" t="n">
-        <v>3</v>
+        <v>16</v>
       </c>
       <c r="J19" s="12" t="n">
-        <v>13</v>
+        <v>0</v>
       </c>
       <c r="K19" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L19" s="12" t="n">
-        <v>18.8</v>
+        <v>100</v>
       </c>
       <c r="M19" s="12" t="n">
         <v>100</v>
@@ -2174,16 +2174,16 @@
         <v>5</v>
       </c>
       <c r="C20" s="12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D20" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="E20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F20" s="12" t="n">
-        <v>40</v>
+        <v>100</v>
       </c>
       <c r="G20" s="12" t="n">
         <v>100</v>
@@ -2192,16 +2192,16 @@
         <v>7</v>
       </c>
       <c r="I20" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J20" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K20" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L20" s="12" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="M20" s="12" t="n">
         <v>100</v>
@@ -2217,16 +2217,16 @@
         <v>1</v>
       </c>
       <c r="C21" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D21" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D21" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="E21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F21" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G21" s="12" t="n">
         <v>100</v>
@@ -2235,16 +2235,16 @@
         <v>2</v>
       </c>
       <c r="I21" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J21" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J21" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="K21" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L21" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M21" s="12" t="n">
         <v>100</v>
@@ -2260,16 +2260,16 @@
         <v>2</v>
       </c>
       <c r="C22" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D22" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D22" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="E22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F22" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G22" s="12" t="n">
         <v>100</v>
@@ -2278,16 +2278,16 @@
         <v>5</v>
       </c>
       <c r="I22" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J22" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J22" s="12" t="n">
-        <v>5</v>
       </c>
       <c r="K22" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L22" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M22" s="12" t="n">
         <v>100</v>
@@ -2303,16 +2303,16 @@
         <v>2</v>
       </c>
       <c r="C23" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D23" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F23" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G23" s="12" t="n">
         <v>100</v>
@@ -2321,16 +2321,16 @@
         <v>5</v>
       </c>
       <c r="I23" s="12" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="J23" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K23" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L23" s="12" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="M23" s="12" t="n">
         <v>100</v>
@@ -2346,16 +2346,16 @@
         <v>1</v>
       </c>
       <c r="C24" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D24" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D24" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="E24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F24" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G24" s="12" t="n">
         <v>100</v>
@@ -2364,16 +2364,16 @@
         <v>2</v>
       </c>
       <c r="I24" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J24" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J24" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="K24" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L24" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M24" s="12" t="n">
         <v>100</v>
@@ -2475,16 +2475,16 @@
         <v>2</v>
       </c>
       <c r="C27" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D27" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D27" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="E27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F27" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G27" s="12" t="n">
         <v>100</v>
@@ -2493,16 +2493,16 @@
         <v>6</v>
       </c>
       <c r="I27" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J27" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J27" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="K27" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L27" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M27" s="12" t="n">
         <v>100</v>
@@ -2518,16 +2518,16 @@
         <v>3</v>
       </c>
       <c r="C28" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="D28" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F28" s="12" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="G28" s="12" t="n">
         <v>100</v>
@@ -2536,16 +2536,16 @@
         <v>7</v>
       </c>
       <c r="I28" s="12" t="n">
-        <v>3</v>
+        <v>7</v>
       </c>
       <c r="J28" s="12" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="K28" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L28" s="12" t="n">
-        <v>42.9</v>
+        <v>100</v>
       </c>
       <c r="M28" s="12" t="n">
         <v>100</v>
@@ -2561,16 +2561,16 @@
         <v>1</v>
       </c>
       <c r="C29" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D29" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D29" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="E29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F29" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G29" s="12" t="n">
         <v>100</v>
@@ -2579,16 +2579,16 @@
         <v>3</v>
       </c>
       <c r="I29" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J29" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J29" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K29" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L29" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M29" s="12" t="n">
         <v>100</v>
@@ -2604,16 +2604,16 @@
         <v>2</v>
       </c>
       <c r="C30" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D30" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F30" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G30" s="12" t="n">
         <v>100</v>
@@ -2622,16 +2622,16 @@
         <v>3</v>
       </c>
       <c r="I30" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J30" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K30" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L30" s="12" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="M30" s="12" t="n">
         <v>100</v>
@@ -2647,16 +2647,16 @@
         <v>1</v>
       </c>
       <c r="C31" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D31" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D31" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="E31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F31" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G31" s="12" t="n">
         <v>100</v>
@@ -2665,16 +2665,16 @@
         <v>2</v>
       </c>
       <c r="I31" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J31" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J31" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="K31" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L31" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M31" s="12" t="n">
         <v>100</v>
@@ -2690,16 +2690,16 @@
         <v>3</v>
       </c>
       <c r="C32" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D32" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D32" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="E32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F32" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G32" s="12" t="n">
         <v>100</v>
@@ -2708,16 +2708,16 @@
         <v>4</v>
       </c>
       <c r="I32" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="J32" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J32" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="K32" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L32" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M32" s="12" t="n">
         <v>100</v>
@@ -2733,16 +2733,16 @@
         <v>2</v>
       </c>
       <c r="C33" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D33" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D33" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="E33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F33" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G33" s="12" t="n">
         <v>100</v>
@@ -2751,16 +2751,16 @@
         <v>2</v>
       </c>
       <c r="I33" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J33" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J33" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="K33" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L33" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M33" s="12" t="n">
         <v>100</v>
@@ -2776,37 +2776,37 @@
         <v>7</v>
       </c>
       <c r="C34" s="12" t="n">
-        <v>1</v>
+        <v>7</v>
       </c>
       <c r="D34" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="E34" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F34" s="12" t="n">
-        <v>14.3</v>
+        <v>100</v>
       </c>
       <c r="G34" s="12" t="n">
-        <v>85.7</v>
+        <v>100</v>
       </c>
       <c r="H34" s="12" t="n">
         <v>10</v>
       </c>
       <c r="I34" s="12" t="n">
-        <v>1</v>
+        <v>10</v>
       </c>
       <c r="J34" s="12" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="K34" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="L34" s="12" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="M34" s="12" t="n">
-        <v>90</v>
+        <v>100</v>
       </c>
     </row>
     <row r="35">
@@ -2819,16 +2819,16 @@
         <v>5</v>
       </c>
       <c r="C35" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="D35" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D35" s="12" t="n">
-        <v>5</v>
       </c>
       <c r="E35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F35" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G35" s="12" t="n">
         <v>100</v>
@@ -2837,16 +2837,16 @@
         <v>5</v>
       </c>
       <c r="I35" s="12" t="n">
+        <v>5</v>
+      </c>
+      <c r="J35" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J35" s="12" t="n">
-        <v>5</v>
       </c>
       <c r="K35" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L35" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M35" s="12" t="n">
         <v>100</v>
@@ -2862,16 +2862,16 @@
         <v>1</v>
       </c>
       <c r="C36" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D36" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D36" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="E36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F36" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G36" s="12" t="n">
         <v>100</v>
@@ -2880,16 +2880,16 @@
         <v>2</v>
       </c>
       <c r="I36" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J36" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J36" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="K36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L36" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M36" s="12" t="n">
         <v>100</v>
@@ -2905,16 +2905,16 @@
         <v>2</v>
       </c>
       <c r="C37" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D37" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D37" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="E37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F37" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G37" s="12" t="n">
         <v>100</v>
@@ -2923,16 +2923,16 @@
         <v>3</v>
       </c>
       <c r="I37" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J37" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J37" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K37" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L37" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M37" s="12" t="n">
         <v>100</v>
@@ -2948,16 +2948,16 @@
         <v>6</v>
       </c>
       <c r="C38" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D38" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D38" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="E38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F38" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G38" s="12" t="n">
         <v>100</v>
@@ -2966,16 +2966,16 @@
         <v>6</v>
       </c>
       <c r="I38" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J38" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J38" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="K38" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L38" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M38" s="12" t="n">
         <v>100</v>
@@ -3077,37 +3077,37 @@
         <v>6</v>
       </c>
       <c r="C41" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D41" s="12" t="n">
-        <v>3</v>
-      </c>
       <c r="E41" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F41" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G41" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="H41" s="12" t="n">
         <v>8</v>
       </c>
       <c r="I41" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J41" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J41" s="12" t="n">
-        <v>5</v>
-      </c>
       <c r="K41" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="L41" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M41" s="12" t="n">
-        <v>62.5</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42">
@@ -3120,37 +3120,37 @@
         <v>5</v>
       </c>
       <c r="C42" s="12" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="D42" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E42" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F42" s="12" t="n">
-        <v>20</v>
+        <v>100</v>
       </c>
       <c r="G42" s="12" t="n">
-        <v>60</v>
+        <v>100</v>
       </c>
       <c r="H42" s="12" t="n">
         <v>6</v>
       </c>
       <c r="I42" s="12" t="n">
-        <v>1</v>
+        <v>6</v>
       </c>
       <c r="J42" s="12" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K42" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L42" s="12" t="n">
-        <v>16.7</v>
+        <v>100</v>
       </c>
       <c r="M42" s="12" t="n">
-        <v>66.7</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43">
@@ -3163,16 +3163,16 @@
         <v>4</v>
       </c>
       <c r="C43" s="12" t="n">
+        <v>4</v>
+      </c>
+      <c r="D43" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D43" s="12" t="n">
-        <v>4</v>
       </c>
       <c r="E43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F43" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G43" s="12" t="n">
         <v>100</v>
@@ -3181,16 +3181,16 @@
         <v>8</v>
       </c>
       <c r="I43" s="12" t="n">
+        <v>8</v>
+      </c>
+      <c r="J43" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J43" s="12" t="n">
-        <v>8</v>
       </c>
       <c r="K43" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L43" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M43" s="12" t="n">
         <v>100</v>
@@ -3206,37 +3206,37 @@
         <v>3</v>
       </c>
       <c r="C44" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="D44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="D44" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="E44" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F44" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G44" s="12" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="H44" s="12" t="n">
         <v>3</v>
       </c>
       <c r="I44" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J44" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="J44" s="12" t="n">
-        <v>1</v>
-      </c>
       <c r="K44" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L44" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M44" s="12" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45">
@@ -3292,37 +3292,37 @@
         <v>1</v>
       </c>
       <c r="C46" s="12" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="E46" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F46" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G46" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="H46" s="12" t="n">
         <v>2</v>
       </c>
       <c r="I46" s="12" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J46" s="12" t="n">
         <v>0</v>
       </c>
       <c r="K46" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="L46" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M46" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47">
@@ -3335,16 +3335,16 @@
         <v>6</v>
       </c>
       <c r="C47" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="D47" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D47" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="E47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F47" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G47" s="12" t="n">
         <v>100</v>
@@ -3353,16 +3353,16 @@
         <v>6</v>
       </c>
       <c r="I47" s="12" t="n">
+        <v>6</v>
+      </c>
+      <c r="J47" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J47" s="12" t="n">
-        <v>6</v>
       </c>
       <c r="K47" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L47" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M47" s="12" t="n">
         <v>100</v>
@@ -3378,16 +3378,16 @@
         <v>2</v>
       </c>
       <c r="C48" s="12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="D48" s="12" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="E48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F48" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G48" s="12" t="n">
         <v>100</v>
@@ -3396,16 +3396,16 @@
         <v>3</v>
       </c>
       <c r="I48" s="12" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="J48" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K48" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L48" s="12" t="n">
-        <v>33.3</v>
+        <v>100</v>
       </c>
       <c r="M48" s="12" t="n">
         <v>100</v>
@@ -3421,16 +3421,16 @@
         <v>4</v>
       </c>
       <c r="C49" s="12" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D49" s="12" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="E49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F49" s="12" t="n">
-        <v>50</v>
+        <v>100</v>
       </c>
       <c r="G49" s="12" t="n">
         <v>100</v>
@@ -3439,16 +3439,16 @@
         <v>9</v>
       </c>
       <c r="I49" s="12" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="J49" s="12" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="K49" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L49" s="12" t="n">
-        <v>44.4</v>
+        <v>100</v>
       </c>
       <c r="M49" s="12" t="n">
         <v>100</v>
@@ -3593,16 +3593,16 @@
         <v>1</v>
       </c>
       <c r="C53" s="12" t="n">
+        <v>1</v>
+      </c>
+      <c r="D53" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D53" s="12" t="n">
-        <v>1</v>
       </c>
       <c r="E53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F53" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G53" s="12" t="n">
         <v>100</v>
@@ -3611,16 +3611,16 @@
         <v>2</v>
       </c>
       <c r="I53" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="J53" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J53" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="K53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L53" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M53" s="12" t="n">
         <v>100</v>
@@ -3636,16 +3636,16 @@
         <v>2</v>
       </c>
       <c r="C54" s="12" t="n">
+        <v>2</v>
+      </c>
+      <c r="D54" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="D54" s="12" t="n">
-        <v>2</v>
       </c>
       <c r="E54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="F54" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="G54" s="12" t="n">
         <v>100</v>
@@ -3654,16 +3654,16 @@
         <v>3</v>
       </c>
       <c r="I54" s="12" t="n">
+        <v>3</v>
+      </c>
+      <c r="J54" s="12" t="n">
         <v>0</v>
-      </c>
-      <c r="J54" s="12" t="n">
-        <v>3</v>
       </c>
       <c r="K54" s="12" t="n">
         <v>0</v>
       </c>
       <c r="L54" s="12" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="M54" s="12" t="n">
         <v>100</v>
@@ -3848,7 +3848,7 @@
       </c>
       <c r="F6" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G6" s="12" t="inlineStr">
@@ -3858,7 +3858,7 @@
       </c>
       <c r="H6" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours scopes records by role and sales unit (Team Lead sees the unit's, AO his own); BDOI adds the Team Head and Unit Head levels of the reporting hierarchy.</t>
+          <t>Data scope tests: an Account Officer sees My Dispositions and his assigned accounts only, a Team Lead the accounts of his units and of every unit under a unit he heads, LAMD and Contact Center users without premium columns; persona menu test of each Renewal role (no Processing Worklist or Renewal Setup for Marketing, no Renewal Advice for LAMD).</t>
         </is>
       </c>
     </row>
@@ -3932,7 +3932,7 @@
       </c>
       <c r="F8" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G8" s="12" t="inlineStr">
@@ -3942,7 +3942,7 @@
       </c>
       <c r="H8" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI ends the session after 30 minutes of inactivity and then shows "Your session timed out"; ours warns 30 minutes before the system log-out, as BRD x.001 reads.</t>
+          <t>Platform session tests of User Access Maintenance: sign-out after the inactivity time with the message Your session timed out. Please log in again to continue, the warning before the system-triggered end of the session, and the session log with the reason; the Renewal screens use the platform session.</t>
         </is>
       </c>
     </row>
@@ -3974,7 +3974,7 @@
       </c>
       <c r="F9" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -3984,7 +3984,7 @@
       </c>
       <c r="H9" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours has Renewal Home, Expiry List, LAMD Reports, Insurer Batches and Letters as separate screens; BDOI puts the bucket lists, uploads (insurer disposition, account update, placement report, hold cover response) and LAMD on one landing page.</t>
+          <t>Renewal module tests: the Processing Team Lead's menu with the Processing Worklist, Insurer Batches and uploads, none of them for a Marketing Account Officer; the same file uploaded twice is refused and nothing is updated; the upload result lists every refused row with its message and downloads.</t>
         </is>
       </c>
     </row>
@@ -4016,7 +4016,7 @@
       </c>
       <c r="F10" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G10" s="12" t="inlineStr">
@@ -4026,7 +4026,7 @@
       </c>
       <c r="H10" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours shows tiles by status, bucket and expiry window that open filtered lists; BDOI adds the period, market segment and Account Officer filters and a fixed drill-down column set.</t>
+          <t>Renewal dashboard tests: open accounts per Account Officer for the Team Lead, Expiring within 30 days opening exactly the accounts counted, every figure and drill-down following the Market Segment filter; production against the Annual Renewal Budget with % vs Budget and variance and Show Details totalling the actual; pipeline and ageing totals equal to the sum of their stages and buckets; closing ratio, Top 50/75/100 open deals, count and YTD persistency, product mix, insurer approval and the KPI cards with their drill-down lists.</t>
         </is>
       </c>
     </row>
@@ -4058,7 +4058,7 @@
       </c>
       <c r="F11" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G11" s="12" t="inlineStr">
@@ -4068,7 +4068,7 @@
       </c>
       <c r="H11" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Premium and commission against budget, variance, growth and adjustments; the system has production against target per team in the New Business dashboard, not a renewal budget.</t>
+          <t>Renewal dashboard tests: open accounts per Account Officer for the Team Lead, Expiring within 30 days opening exactly the accounts counted, every figure and drill-down following the Market Segment filter; production against the Annual Renewal Budget with % vs Budget and variance and Show Details totalling the actual; pipeline and ageing totals equal to the sum of their stages and buckets; closing ratio, Top 50/75/100 open deals, count and YTD persistency, product mix, insurer approval and the KPI cards with their drill-down lists.</t>
         </is>
       </c>
     </row>
@@ -4100,7 +4100,7 @@
       </c>
       <c r="F12" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G12" s="12" t="inlineStr">
@@ -4110,7 +4110,7 @@
       </c>
       <c r="H12" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Pipeline by business type (New, Organic, Submitted, Renewal, Deferred) and stages For Survey to For Delivery; the the system stages have other names.</t>
+          <t>Renewal dashboard tests: open accounts per Account Officer for the Team Lead, Expiring within 30 days opening exactly the accounts counted, every figure and drill-down following the Market Segment filter; production against the Annual Renewal Budget with % vs Budget and variance and Show Details totalling the actual; pipeline and ageing totals equal to the sum of their stages and buckets; closing ratio, Top 50/75/100 open deals, count and YTD persistency, product mix, insurer approval and the KPI cards with their drill-down lists.</t>
         </is>
       </c>
     </row>
@@ -4142,7 +4142,7 @@
       </c>
       <c r="F13" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G13" s="12" t="inlineStr">
@@ -4152,7 +4152,7 @@
       </c>
       <c r="H13" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours counts accounts expiring in 30, 60, 90 and 140 days; BDOI ages unrenewed accounts by month (prior, current, +1, +2) with premium and commission.</t>
+          <t>Renewal dashboard tests: open accounts per Account Officer for the Team Lead, Expiring within 30 days opening exactly the accounts counted, every figure and drill-down following the Market Segment filter; production against the Annual Renewal Budget with % vs Budget and variance and Show Details totalling the actual; pipeline and ageing totals equal to the sum of their stages and buckets; closing ratio, Top 50/75/100 open deals, count and YTD persistency, product mix, insurer approval and the KPI cards with their drill-down lists.</t>
         </is>
       </c>
     </row>
@@ -4184,7 +4184,7 @@
       </c>
       <c r="F14" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G14" s="12" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="H14" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Closing ratio by business type (booked over total accounts) with the in-process, posted and booked pipeline tiers.</t>
+          <t>Renewal dashboard tests: open accounts per Account Officer for the Team Lead, Expiring within 30 days opening exactly the accounts counted, every figure and drill-down following the Market Segment filter; production against the Annual Renewal Budget with % vs Budget and variance and Show Details totalling the actual; pipeline and ageing totals equal to the sum of their stages and buckets; closing ratio, Top 50/75/100 open deals, count and YTD persistency, product mix, insurer approval and the KPI cards with their drill-down lists.</t>
         </is>
       </c>
     </row>
@@ -4226,7 +4226,7 @@
       </c>
       <c r="F15" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G15" s="12" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="H15" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Top 50, 75 or 100 open deals by premium.</t>
+          <t>Renewal dashboard tests: open accounts per Account Officer for the Team Lead, Expiring within 30 days opening exactly the accounts counted, every figure and drill-down following the Market Segment filter; production against the Annual Renewal Budget with % vs Budget and variance and Show Details totalling the actual; pipeline and ageing totals equal to the sum of their stages and buckets; closing ratio, Top 50/75/100 open deals, count and YTD persistency, product mix, insurer approval and the KPI cards with their drill-down lists.</t>
         </is>
       </c>
     </row>
@@ -4268,7 +4268,7 @@
       </c>
       <c r="F16" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -4278,7 +4278,7 @@
       </c>
       <c r="H16" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Renewal persistency by count, premium and commission for six months and year to date; the system has a persistency report for submitted policies only.</t>
+          <t>Renewal dashboard tests: open accounts per Account Officer for the Team Lead, Expiring within 30 days opening exactly the accounts counted, every figure and drill-down following the Market Segment filter; production against the Annual Renewal Budget with % vs Budget and variance and Show Details totalling the actual; pipeline and ageing totals equal to the sum of their stages and buckets; closing ratio, Top 50/75/100 open deals, count and YTD persistency, product mix, insurer approval and the KPI cards with their drill-down lists.</t>
         </is>
       </c>
     </row>
@@ -4310,7 +4310,7 @@
       </c>
       <c r="F17" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G17" s="12" t="inlineStr">
@@ -4320,7 +4320,7 @@
       </c>
       <c r="H17" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Production by product line on the dashboard; the system reports production per unit and officer in New Business, not by product line.</t>
+          <t>Renewal dashboard tests: open accounts per Account Officer for the Team Lead, Expiring within 30 days opening exactly the accounts counted, every figure and drill-down following the Market Segment filter; production against the Annual Renewal Budget with % vs Budget and variance and Show Details totalling the actual; pipeline and ageing totals equal to the sum of their stages and buckets; closing ratio, Top 50/75/100 open deals, count and YTD persistency, product mix, insurer approval and the KPI cards with their drill-down lists.</t>
         </is>
       </c>
     </row>
@@ -4352,7 +4352,7 @@
       </c>
       <c r="F18" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G18" s="12" t="inlineStr">
@@ -4362,7 +4362,7 @@
       </c>
       <c r="H18" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours shows overdue insurer batches and the insurer extract; BDOI adds the approval monitoring table (Renew As Is, approved, pending, returned, % approval) and pending accounts per insurer.</t>
+          <t>Renewal dashboard tests: open accounts per Account Officer for the Team Lead, Expiring within 30 days opening exactly the accounts counted, every figure and drill-down following the Market Segment filter; production against the Annual Renewal Budget with % vs Budget and variance and Show Details totalling the actual; pipeline and ageing totals equal to the sum of their stages and buckets; closing ratio, Top 50/75/100 open deals, count and YTD persistency, product mix, insurer approval and the KPI cards with their drill-down lists.</t>
         </is>
       </c>
     </row>
@@ -4394,7 +4394,7 @@
       </c>
       <c r="F19" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G19" s="12" t="inlineStr">
@@ -4404,7 +4404,7 @@
       </c>
       <c r="H19" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours has 34 summary counters of the status report and the home tiles; BDOI adds cards from Cashiering (bounced checks, unapplied payments, refunds) and hold covers expiring in 7 days.</t>
+          <t>Renewal dashboard tests: open accounts per Account Officer for the Team Lead, Expiring within 30 days opening exactly the accounts counted, every figure and drill-down following the Market Segment filter; production against the Annual Renewal Budget with % vs Budget and variance and Show Details totalling the actual; pipeline and ageing totals equal to the sum of their stages and buckets; closing ratio, Top 50/75/100 open deals, count and YTD persistency, product mix, insurer approval and the KPI cards with their drill-down lists.</t>
         </is>
       </c>
     </row>
@@ -4436,7 +4436,7 @@
       </c>
       <c r="F20" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G20" s="12" t="inlineStr">
@@ -4446,7 +4446,7 @@
       </c>
       <c r="H20" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI shows four panels Clean, Review, Non-Renewable and All; ours shows tabs by disposition and an Exceptions tab, with the Clean / Review / Exception pill (BRRN.023).</t>
+          <t>Renewal Accounts panel tests: Clean, Review, Non-Renewable and All panels with BDOI's columns and sort, continuous scrolling with the row count, the Claims flag never in Clean, the padlock of a locked account; list export to Excel, PDF and CSV.</t>
         </is>
       </c>
     </row>
@@ -4562,7 +4562,7 @@
       </c>
       <c r="F23" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G23" s="12" t="inlineStr">
@@ -4572,7 +4572,7 @@
       </c>
       <c r="H23" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI wants one processing dashboard for New Business and Renewal with a combined view; ours has the Processing Team Lead view per officer on Renewal Home.</t>
+          <t>Processing dashboard tests: Combined View equal to New Business View plus Renewal View, open accounts per Processing Officer for the Processing Team Lead.</t>
         </is>
       </c>
     </row>
@@ -4604,7 +4604,7 @@
       </c>
       <c r="F24" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G24" s="12" t="inlineStr">
@@ -4614,7 +4614,7 @@
       </c>
       <c r="H24" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: KPI cards For Placement, For Booking, With and Without Policy, For Releasing, Released, Unreleased, Directly Booked, Returned; the system shows these queues on the New Business placement, booking and e-policy screens, not as cards.</t>
+          <t>Processing KPI card tests: For Placement, For Booking, With and Without Policy, Released and Unreleased with the reason, Directly Booked and Returned Accounts with the return reason, the ageing in business days from submission or sending, Unassigned and Assigned tabs with the Placement Processor, TAT Status Beyond TAT; each card lists exactly the accounts counted with search, filter, sort and export.</t>
         </is>
       </c>
     </row>
@@ -4646,7 +4646,7 @@
       </c>
       <c r="F25" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G25" s="12" t="inlineStr">
@@ -4656,7 +4656,7 @@
       </c>
       <c r="H25" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Assigned and Unassigned tabs with ageing in business days from Submitted for Placement.</t>
+          <t>Processing KPI card tests: For Placement, For Booking, With and Without Policy, Released and Unreleased with the reason, Directly Booked and Returned Accounts with the return reason, the ageing in business days from submission or sending, Unassigned and Assigned tabs with the Placement Processor, TAT Status Beyond TAT; each card lists exactly the accounts counted with search, filter, sort and export.</t>
         </is>
       </c>
     </row>
@@ -4688,7 +4688,7 @@
       </c>
       <c r="F26" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G26" s="12" t="inlineStr">
@@ -4698,7 +4698,7 @@
       </c>
       <c r="H26" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: For Booking drill-down with ageing from the placement date.</t>
+          <t>Processing KPI card tests: For Placement, For Booking, With and Without Policy, Released and Unreleased with the reason, Directly Booked and Returned Accounts with the return reason, the ageing in business days from submission or sending, Unassigned and Assigned tabs with the Placement Processor, TAT Status Beyond TAT; each card lists exactly the accounts counted with search, filter, sort and export.</t>
         </is>
       </c>
     </row>
@@ -4730,7 +4730,7 @@
       </c>
       <c r="F27" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G27" s="12" t="inlineStr">
@@ -4740,7 +4740,7 @@
       </c>
       <c r="H27" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: With / Without Policy drill-down with policy status, TAT status, placement issue and resolution date.</t>
+          <t>Processing KPI card tests: For Placement, For Booking, With and Without Policy, Released and Unreleased with the reason, Directly Booked and Returned Accounts with the return reason, the ageing in business days from submission or sending, Unassigned and Assigned tabs with the Placement Processor, TAT Status Beyond TAT; each card lists exactly the accounts counted with search, filter, sort and export.</t>
         </is>
       </c>
     </row>
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F28" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G28" s="12" t="inlineStr">
@@ -4782,7 +4782,7 @@
       </c>
       <c r="H28" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Policy transmittal drill-down (sent, pending, unsuccessful) with reason for reject.</t>
+          <t>Processing KPI card tests: For Placement, For Booking, With and Without Policy, Released and Unreleased with the reason, Directly Booked and Returned Accounts with the return reason, the ageing in business days from submission or sending, Unassigned and Assigned tabs with the Placement Processor, TAT Status Beyond TAT; each card lists exactly the accounts counted with search, filter, sort and export.</t>
         </is>
       </c>
     </row>
@@ -4814,7 +4814,7 @@
       </c>
       <c r="F29" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G29" s="12" t="inlineStr">
@@ -4824,7 +4824,7 @@
       </c>
       <c r="H29" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Direct Booking drill-down; the system books directly in New Business.</t>
+          <t>Processing KPI card tests: For Placement, For Booking, With and Without Policy, Released and Unreleased with the reason, Directly Booked and Returned Accounts with the return reason, the ageing in business days from submission or sending, Unassigned and Assigned tabs with the Placement Processor, TAT Status Beyond TAT; each card lists exactly the accounts counted with search, filter, sort and export.</t>
         </is>
       </c>
     </row>
@@ -4856,7 +4856,7 @@
       </c>
       <c r="F30" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G30" s="12" t="inlineStr">
@@ -4866,7 +4866,7 @@
       </c>
       <c r="H30" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours flags returned accounts and filters them; BDOI adds a Returned card with the reason for return.</t>
+          <t>Processing KPI card tests: For Placement, For Booking, With and Without Policy, Released and Unreleased with the reason, Directly Booked and Returned Accounts with the return reason, the ageing in business days from submission or sending, Unassigned and Assigned tabs with the Placement Processor, TAT Status Beyond TAT; each card lists exactly the accounts counted with search, filter, sort and export.</t>
         </is>
       </c>
     </row>
@@ -5108,7 +5108,7 @@
       </c>
       <c r="F36" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G36" s="12" t="inlineStr">
@@ -5118,7 +5118,7 @@
       </c>
       <c r="H36" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI creates a renewal account per listed account at generation (disposition For Disposition, status In Process Renewal); ours creates a renewal record with a renewal reference, starts nothing until an explicit initiation (BRRN.021) and creates the renewal account when processing starts. BDOI also lists Free-First-Year accounts in process.</t>
+          <t>RMEL generation tests: a booked account expiring at the lead days is listed once with its renewal reference even after a second run, a change of the lead days applies at the next run, HMO accounts are left out, No records found. and Generation of RMEL successful! messages.</t>
         </is>
       </c>
     </row>
@@ -5150,7 +5150,7 @@
       </c>
       <c r="F37" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G37" s="12" t="inlineStr">
@@ -5160,7 +5160,7 @@
       </c>
       <c r="H37" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI offers a Refresh Endorsements action that re-reads the mother policy and recalculates; ours creates the renewal account from the policy as of the last posted endorsement and blocks post and RA while an endorsement is in progress.</t>
+          <t>Endorsement synchronisation tests: posting is refused while an endorsement of the expiring policy is open and the message names it; Refresh Endorsements brings the endorsed sum insured and the endorsement number to the renewal account.</t>
         </is>
       </c>
     </row>
@@ -5192,7 +5192,7 @@
       </c>
       <c r="F38" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G38" s="12" t="inlineStr">
@@ -5202,7 +5202,7 @@
       </c>
       <c r="H38" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Same export and print; BDOI fixes the file name RMEL_&lt;MMM&gt;_&lt;YYYY&gt;_&lt;MMDDYYYY&gt;.xlsx, ours does not name the file.</t>
+          <t>RMEL export tests: the file named RMEL_&lt;Month&gt;_&lt;Year&gt;_&lt;MMDDYYYY&gt;.xlsx with the rows and columns of the screen; the RMEL report of the Report Centre printed with the paper size and orientation chosen in the print options.</t>
         </is>
       </c>
     </row>
@@ -5234,7 +5234,7 @@
       </c>
       <c r="F39" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G39" s="12" t="inlineStr">
@@ -5244,7 +5244,7 @@
       </c>
       <c r="H39" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours creates the renewal account from a renewal record (Create Renewal Account on the record); BDOI lets a user create a renewal account for any expiring account, inception one day after the old expiry and expiry one year later, then sanitises it. Ours keeps the term of the expiring policy.</t>
+          <t>Create Renewal Account tests: a renewal account from an expiring Motor account with the same client, vehicle, insurer and PN, the business type Renewal and the link to the expiring account; every missing mandatory field named; the new account goes through sanitation, assignment and classification.</t>
         </is>
       </c>
     </row>
@@ -5276,7 +5276,7 @@
       </c>
       <c r="F40" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G40" s="12" t="inlineStr">
@@ -5286,7 +5286,7 @@
       </c>
       <c r="H40" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours checks that no other open renewal exists for the same expiring policy; BDOI checks client number, risk code, PN and expiring policy number (configurable per line, Annex B), tells exact from potential duplicates, warns on manual creation and puts generated ones in Review with a link; a cancelled match does not block.</t>
+          <t>Duplicate checking tests: the potential-duplicate warning on the same plate, serial and motor numbers and an overlapping period, the cancelled-match warning with the save allowed, a generated duplicate For Review with the reason Potential Duplicate Account and the link.</t>
         </is>
       </c>
     </row>
@@ -5360,7 +5360,7 @@
       </c>
       <c r="F42" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G42" s="12" t="inlineStr">
@@ -5370,7 +5370,7 @@
       </c>
       <c r="H42" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Several rules differ: missing data is Review in BDOI and Exception in ours; TSI above PHP 250M is Clean / For Quotation in BDOI and Review / For Proposal in ours; any endorsement is Review in BDOI, only an endorsement in progress blocks in ours; PA and GPA are Clean / For Proposal in BDOI only; a total loss is Not for Renewal in BDOI, a manual reason in ours until Claims gives the indicator.</t>
+          <t>Sanitation rule tests per market segment: above the sum insured threshold For Quotation to the TSU, personal accident lines For Proposal, Risk Code is not maintained as Renewable/Not Renewable to Review, a non-renewable risk code Not for Renewal and out of the assignment list, a CBG Motor account without PN not Clean.</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5402,7 @@
       </c>
       <c r="F43" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G43" s="12" t="inlineStr">
@@ -5412,7 +5412,7 @@
       </c>
       <c r="H43" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Third bucket Non-Renewable (BDOI) against Exception (ours, BRRN.023); BDOI sets Clean accounts For Renewal with status For RA Generation (CBG) or Posted (Non-CBG); ours lets the decision matrix propose or apply the disposition and a failed check can never be Clean.</t>
+          <t>Classification tests: an open claim always Review, Clean at the next evaluation once the claim is closed with both classifications in the history, a manual reclassification to Clean refused when a rule failed, the rule version and the rule shown per classification.</t>
         </is>
       </c>
     </row>
@@ -5444,7 +5444,7 @@
       </c>
       <c r="F44" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G44" s="12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="H44" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Automatic CBG Motor renewal values (Annexes D and E: depreciation, BI/PD tiers, Auto Promo to Regular, DST, VAT, LGT); ours rates the renewal account on the package of the expiring account. BDOI's list for CBG Home and Non-CBG is empty.</t>
+          <t>CBG Motor automatic update tests: the Computations tab with the expiring values and the differences, own damage and theft sum insured depreciated by 10% for a Regular renewal with the other fields of Annex D, the financial impact flagged with the difference.</t>
         </is>
       </c>
     </row>
@@ -5486,7 +5486,7 @@
       </c>
       <c r="F45" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G45" s="12" t="inlineStr">
@@ -5496,7 +5496,7 @@
       </c>
       <c r="H45" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI assigns automatically by team and sub-team with round robin (Annex F) for Marketing and Processing; ours lets the Team Lead assign (BRD 1.005, 3.005) and does not assign CBG accounts.</t>
+          <t>Automatic assignment tests: accounts assigned per segment to the Account Officer with the fewest open accounts and then in turn appear in his My Dispositions and leave the unassigned list, no assignment to an officer of another unit, the notice &lt;reference&gt; assigned to you.</t>
         </is>
       </c>
     </row>
@@ -5570,7 +5570,7 @@
       </c>
       <c r="F47" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G47" s="12" t="inlineStr">
@@ -5580,7 +5580,7 @@
       </c>
       <c r="H47" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI's transfer is a referral: the renewal stays with its unit and the receiving unit opens a New Business account; ours moves the renewal to the receiving unit (BRD 1.006, 1.007, 2.005).</t>
+          <t>Transfer request tests: a referral never changes the owner of the renewal account; Transfer Request Number with Pending Acceptance and the receiving Team Leads notified, a request to the own unit refused, acceptance with its date and time, rejection without remarks refused, the New Business account created from the copied data and linked to the request, Transfer Request Monitoring with the New Business account number, the audit log of every step and the requester notified of a rejection or return.</t>
         </is>
       </c>
     </row>
@@ -5612,7 +5612,7 @@
       </c>
       <c r="F48" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G48" s="12" t="inlineStr">
@@ -5622,7 +5622,7 @@
       </c>
       <c r="H48" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Same request with target unit and justification; BDOI adds a Transfer Request Number and status Pending Acceptance.</t>
+          <t>Transfer request tests: a referral never changes the owner of the renewal account; Transfer Request Number with Pending Acceptance and the receiving Team Leads notified, a request to the own unit refused, acceptance with its date and time, rejection without remarks refused, the New Business account created from the copied data and linked to the request, Transfer Request Monitoring with the New Business account number, the audit log of every step and the requester notified of a rejection or return.</t>
         </is>
       </c>
     </row>
@@ -5654,7 +5654,7 @@
       </c>
       <c r="F49" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G49" s="12" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="H49" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours accepts or declines with remarks; BDOI adds Return for Clarification.</t>
+          <t>Transfer request tests: a referral never changes the owner of the renewal account; Transfer Request Number with Pending Acceptance and the receiving Team Leads notified, a request to the own unit refused, acceptance with its date and time, rejection without remarks refused, the New Business account created from the copied data and linked to the request, Transfer Request Monitoring with the New Business account number, the audit log of every step and the requester notified of a rejection or return.</t>
         </is>
       </c>
     </row>
@@ -5696,7 +5696,7 @@
       </c>
       <c r="F50" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G50" s="12" t="inlineStr">
@@ -5706,7 +5706,7 @@
       </c>
       <c r="H50" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Creation of a New Business account from the copied renewal data on acceptance.</t>
+          <t>Transfer request tests: a referral never changes the owner of the renewal account; Transfer Request Number with Pending Acceptance and the receiving Team Leads notified, a request to the own unit refused, acceptance with its date and time, rejection without remarks refused, the New Business account created from the copied data and linked to the request, Transfer Request Monitoring with the New Business account number, the audit log of every step and the requester notified of a rejection or return.</t>
         </is>
       </c>
     </row>
@@ -5738,7 +5738,7 @@
       </c>
       <c r="F51" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G51" s="12" t="inlineStr">
@@ -5748,7 +5748,7 @@
       </c>
       <c r="H51" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours has Transfers (incoming and outgoing); BDOI lists the statuses Draft to Returned for Clarification and the New Business account number.</t>
+          <t>Transfer request tests: a referral never changes the owner of the renewal account; Transfer Request Number with Pending Acceptance and the receiving Team Leads notified, a request to the own unit refused, acceptance with its date and time, rejection without remarks refused, the New Business account created from the copied data and linked to the request, Transfer Request Monitoring with the New Business account number, the audit log of every step and the requester notified of a rejection or return.</t>
         </is>
       </c>
     </row>
@@ -5780,7 +5780,7 @@
       </c>
       <c r="F52" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G52" s="12" t="inlineStr">
@@ -5790,7 +5790,7 @@
       </c>
       <c r="H52" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours notifies the request and the decision; BDOI also notifies a return for clarification.</t>
+          <t>Transfer request tests: a referral never changes the owner of the renewal account; Transfer Request Number with Pending Acceptance and the receiving Team Leads notified, a request to the own unit refused, acceptance with its date and time, rejection without remarks refused, the New Business account created from the copied data and linked to the request, Transfer Request Monitoring with the New Business account number, the audit log of every step and the requester notified of a rejection or return.</t>
         </is>
       </c>
     </row>
@@ -5822,7 +5822,7 @@
       </c>
       <c r="F53" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G53" s="12" t="inlineStr">
@@ -5832,7 +5832,7 @@
       </c>
       <c r="H53" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours uploads LAMD reports of paid-off and RMU loans; BDOI uploads the full CBG loan list (excluding personal loans) and the paid-off list and derives the loan status (Active, Loan Fully Paid, RMU, Unmatched); required fields PN and AO code, plus serial and motor number for Motor.</t>
+          <t>LAMD and BDOFC/SOLD upload tests: the success message of a processed report, the invalid format and missing-required-data refusals, paid-off and RMU matching on the PN and the motor serial and motor numbers with the Annex C rules, a PN on two accounts updating neither, one summary row per upload latest first with the Processing Result workbook, the record-level view filtered by Matched and Unmatched, the paid-off repository keeping an account once.</t>
         </is>
       </c>
     </row>
@@ -5864,7 +5864,7 @@
       </c>
       <c r="F54" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G54" s="12" t="inlineStr">
@@ -5874,7 +5874,7 @@
       </c>
       <c r="H54" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours matches on PN; BDOI matches CBG Motor on PN, serial number and motor number.</t>
+          <t>LAMD and BDOFC/SOLD upload tests: the success message of a processed report, the invalid format and missing-required-data refusals, paid-off and RMU matching on the PN and the motor serial and motor numbers with the Annex C rules, a PN on two accounts updating neither, one summary row per upload latest first with the Processing Result workbook, the record-level view filtered by Matched and Unmatched, the paid-off repository keeping an account once.</t>
         </is>
       </c>
     </row>
@@ -5906,7 +5906,7 @@
       </c>
       <c r="F55" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G55" s="12" t="inlineStr">
@@ -5916,7 +5916,7 @@
       </c>
       <c r="H55" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours shows the match results of each report; BDOI fixes the file-level summary columns, statuses and the result file name.</t>
+          <t>LAMD and BDOFC/SOLD upload tests: the success message of a processed report, the invalid format and missing-required-data refusals, paid-off and RMU matching on the PN and the motor serial and motor numbers with the Annex C rules, a PN on two accounts updating neither, one summary row per upload latest first with the Processing Result workbook, the record-level view filtered by Matched and Unmatched, the paid-off repository keeping an account once.</t>
         </is>
       </c>
     </row>
@@ -5948,7 +5948,7 @@
       </c>
       <c r="F56" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G56" s="12" t="inlineStr">
@@ -5958,7 +5958,7 @@
       </c>
       <c r="H56" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Record-level results with matching and processing status and the reason.</t>
+          <t>LAMD and BDOFC/SOLD upload tests: the success message of a processed report, the invalid format and missing-required-data refusals, paid-off and RMU matching on the PN and the motor serial and motor numbers with the Annex C rules, a PN on two accounts updating neither, one summary row per upload latest first with the Processing Result workbook, the record-level view filtered by Matched and Unmatched, the paid-off repository keeping an account once.</t>
         </is>
       </c>
     </row>
@@ -5990,7 +5990,7 @@
       </c>
       <c r="F57" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G57" s="12" t="inlineStr">
@@ -6000,7 +6000,7 @@
       </c>
       <c r="H57" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI keeps a cumulative list of paid-off accounts without duplicates; ours keeps the lines of each report.</t>
+          <t>LAMD and BDOFC/SOLD upload tests: the success message of a processed report, the invalid format and missing-required-data refusals, paid-off and RMU matching on the PN and the motor serial and motor numbers with the Annex C rules, a PN on two accounts updating neither, one summary row per upload latest first with the Processing Result workbook, the record-level view filtered by Matched and Unmatched, the paid-off repository keeping an account once.</t>
         </is>
       </c>
     </row>
@@ -6032,7 +6032,7 @@
       </c>
       <c r="F58" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G58" s="12" t="inlineStr">
@@ -6042,7 +6042,7 @@
       </c>
       <c r="H58" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOFC and BDOSOLD report upload (PN, assured's name, remarks).</t>
+          <t>LAMD and BDOFC/SOLD upload tests: the success message of a processed report, the invalid format and missing-required-data refusals, paid-off and RMU matching on the PN and the motor serial and motor numbers with the Annex C rules, a PN on two accounts updating neither, one summary row per upload latest first with the Processing Result workbook, the record-level view filtered by Matched and Unmatched, the paid-off repository keeping an account once.</t>
         </is>
       </c>
     </row>
@@ -6074,7 +6074,7 @@
       </c>
       <c r="F59" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G59" s="12" t="inlineStr">
@@ -6084,7 +6084,7 @@
       </c>
       <c r="H59" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOFC / SOLD matching on PN; BDOI does not say what a match changes.</t>
+          <t>LAMD and BDOFC/SOLD upload tests: the success message of a processed report, the invalid format and missing-required-data refusals, paid-off and RMU matching on the PN and the motor serial and motor numbers with the Annex C rules, a PN on two accounts updating neither, one summary row per upload latest first with the Processing Result workbook, the record-level view filtered by Matched and Unmatched, the paid-off repository keeping an account once.</t>
         </is>
       </c>
     </row>
@@ -6116,7 +6116,7 @@
       </c>
       <c r="F60" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G60" s="12" t="inlineStr">
@@ -6126,7 +6126,7 @@
       </c>
       <c r="H60" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Upload summary of the BDOFC / SOLD files.</t>
+          <t>LAMD and BDOFC/SOLD upload tests: the success message of a processed report, the invalid format and missing-required-data refusals, paid-off and RMU matching on the PN and the motor serial and motor numbers with the Annex C rules, a PN on two accounts updating neither, one summary row per upload latest first with the Processing Result workbook, the record-level view filtered by Matched and Unmatched, the paid-off repository keeping an account once.</t>
         </is>
       </c>
     </row>
@@ -6158,7 +6158,7 @@
       </c>
       <c r="F61" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G61" s="12" t="inlineStr">
@@ -6168,7 +6168,7 @@
       </c>
       <c r="H61" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Record-level results of the BDOFC / SOLD files.</t>
+          <t>LAMD and BDOFC/SOLD upload tests: the success message of a processed report, the invalid format and missing-required-data refusals, paid-off and RMU matching on the PN and the motor serial and motor numbers with the Annex C rules, a PN on two accounts updating neither, one summary row per upload latest first with the Processing Result workbook, the record-level view filtered by Matched and Unmatched, the paid-off repository keeping an account once.</t>
         </is>
       </c>
     </row>
@@ -6200,7 +6200,7 @@
       </c>
       <c r="F62" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G62" s="12" t="inlineStr">
@@ -6210,7 +6210,7 @@
       </c>
       <c r="H62" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours uploads the insurer's response file keyed by the renewal reference; BDOI fixes the CBG layout of Annex H (17 fields) and a Non-CBG layout, with its messages.</t>
+          <t>Insurer disposition upload tests: the Annex H layout processed with the success messages, a missing required field refusing the file, Renew As Is setting Clean and For Renewal with premium and terms unchanged, a different expiring policy number flagged for review, Renew with surcharge setting Review, For Disposition and the financial impact.</t>
         </is>
       </c>
     </row>
@@ -6242,7 +6242,7 @@
       </c>
       <c r="F63" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G63" s="12" t="inlineStr">
@@ -6252,7 +6252,7 @@
       </c>
       <c r="H63" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI maps nine insurer dispositions to bucket and disposition (Rejected goes to Review / For Disposition, Total Loss to Non-Renewable); ours has three responses (Renew As Is, Revise, Reject; Reject tags Not for Renewal or returns to Marketing).</t>
+          <t>Insurer disposition upload tests: the Annex H layout processed with the success messages, a missing required field refusing the file, Renew As Is setting Clean and For Renewal with premium and terms unchanged, a different expiring policy number flagged for review, Renew with surcharge setting Review, For Disposition and the financial impact.</t>
         </is>
       </c>
     </row>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="F64" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G64" s="12" t="inlineStr">
@@ -6294,7 +6294,7 @@
       </c>
       <c r="H64" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Upload summary of the insurer disposition files (numbered 012.03 inside FRRN.013 in BDOI's FRS).</t>
+          <t>Insurer disposition upload summary test: one row per upload with its status and counts, latest first.</t>
         </is>
       </c>
     </row>
@@ -6326,7 +6326,7 @@
       </c>
       <c r="F65" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G65" s="12" t="inlineStr">
@@ -6336,7 +6336,7 @@
       </c>
       <c r="H65" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Record-level view with "Record not found" (numbered 012.04 inside FRRN.013).</t>
+          <t>Insurer disposition record-level test: a reference not found is listed with Record not found and updates nothing.</t>
         </is>
       </c>
     </row>
@@ -6368,7 +6368,7 @@
       </c>
       <c r="F66" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G66" s="12" t="inlineStr">
@@ -6378,7 +6378,7 @@
       </c>
       <c r="H66" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Both show every renewal field and the account history (policies, endorsements, payments, claims) with download and print; BDOI adds the refund link.</t>
+          <t>Renewal account detail tests: every RMEL field of the account, the download Renewal Account Details.xlsx, the Account History with the previous ARN, endorsements, payments and claims, a disposition refused until the Account History is opened.</t>
         </is>
       </c>
     </row>
@@ -6410,7 +6410,7 @@
       </c>
       <c r="F67" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G67" s="12" t="inlineStr">
@@ -6420,7 +6420,7 @@
       </c>
       <c r="H67" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours has five dispositions (with Lost Business) and ten non-renewal reasons and locks the account when the RA is generated (BRD 2.004.9); BDOI has four dispositions, 21 reasons and locks when posted and placed. File types and messages are BDOI's.</t>
+          <t>Disposition tests: For Renewal saved and submitted to the Team Lead's review list, Not for Renewal without reason and Booked to New Invoice without an invoice refused, remarks with the user, date and time and at most 200 characters, no change after the Renewal Advice is generated.</t>
         </is>
       </c>
     </row>
@@ -6452,7 +6452,7 @@
       </c>
       <c r="F68" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G68" s="12" t="inlineStr">
@@ -6462,7 +6462,7 @@
       </c>
       <c r="H68" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Allocation of the renewal to several insurers by percentage (total 100%) or amount (total = TSI); the system takes the insurers and shares from the package.</t>
+          <t>Multiple insurer allocation tests: shares of 60% and 40% saved and 60% and 30% refused, coverage amounts totalling the sum insured with the premium computed per insurer.</t>
         </is>
       </c>
     </row>
@@ -6494,7 +6494,7 @@
       </c>
       <c r="F69" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G69" s="12" t="inlineStr">
@@ -6504,7 +6504,7 @@
       </c>
       <c r="H69" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: For Booking Only tag with policy number, OR number, policy document and full payment checks and an override approval; the system books directly in New Business.</t>
+          <t>For Booking Only tests: an account not fully paid cannot be submitted and shows The account is not fully paid. Override approval is required, the override by another user with a justification in the audit log, the account then submitted.</t>
         </is>
       </c>
     </row>
@@ -6536,7 +6536,7 @@
       </c>
       <c r="F70" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G70" s="12" t="inlineStr">
@@ -6546,7 +6546,7 @@
       </c>
       <c r="H70" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Direct-to-Insurer Payment tag with blanket approval or Unit Head approval; the system has the direct payment tag of New Business without the approval route. Ours has only the non-renewal reason Direct to Insurer.</t>
+          <t>Direct-to-Insurer Payment tests: Route for UH Approval sends the account to the Unit Head of the assigned user and it proceeds only once approved; a rejection without reason refused; after a rejection the account proceeds only once the tag is removed.</t>
         </is>
       </c>
     </row>
@@ -6620,7 +6620,7 @@
       </c>
       <c r="F72" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G72" s="12" t="inlineStr">
@@ -6630,7 +6630,7 @@
       </c>
       <c r="H72" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours uploads dispositioned files on the Processing Worklist; BDOI has a general Renewal Update upload with a downloadable template on the landing page.</t>
+          <t>Renewal Update upload tests: a file with unknown references updating the other rows and listing the refused rows with their message, two files giving two results, one summary row per upload latest first, the record-level view with filter, sort and search.</t>
         </is>
       </c>
     </row>
@@ -6672,7 +6672,7 @@
       </c>
       <c r="H73" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Rows matched on the reference number (ours: the renewal reference, mandatory).</t>
+          <t>Renewal Update upload tests: a file with unknown references updating the other rows and listing the refused rows with their message, two files giving two results, one summary row per upload latest first, the record-level view with filter, sort and search.</t>
         </is>
       </c>
     </row>
@@ -6704,7 +6704,7 @@
       </c>
       <c r="F74" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G74" s="12" t="inlineStr">
@@ -6714,7 +6714,7 @@
       </c>
       <c r="H74" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Upload summary columns and statuses.</t>
+          <t>Renewal Update upload tests: a file with unknown references updating the other rows and listing the refused rows with their message, two files giving two results, one summary row per upload latest first, the record-level view with filter, sort and search.</t>
         </is>
       </c>
     </row>
@@ -6746,7 +6746,7 @@
       </c>
       <c r="F75" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G75" s="12" t="inlineStr">
@@ -6756,7 +6756,7 @@
       </c>
       <c r="H75" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Record-level results with filter, sort and search.</t>
+          <t>Renewal Update upload tests: a file with unknown references updating the other rows and listing the refused rows with their message, two files giving two results, one summary row per upload latest first, the record-level view with filter, sort and search.</t>
         </is>
       </c>
     </row>
@@ -6788,7 +6788,7 @@
       </c>
       <c r="F76" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G76" s="12" t="inlineStr">
@@ -6798,7 +6798,7 @@
       </c>
       <c r="H76" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours pushes the account to the unit's TLs (Review in Progress); BDOI makes the user pick the approver and names the status Submitted for Posting.</t>
+          <t>Submission for posting tests: the status Submitted for Posting listed for the approver chosen, every missing required field named with the status unchanged.</t>
         </is>
       </c>
     </row>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="F77" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G77" s="12" t="inlineStr">
@@ -6840,7 +6840,7 @@
       </c>
       <c r="H77" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours sends For Quotation and For Proposal to the New Business quotation or proposal request; BDOI generates a Quick or Full Proposal from the renewal with file names and two or three signatories by TSI (500M).</t>
+          <t>Proposal tests: Generate Proposal Slip only for For Proposal, a Full Proposal of a non-package account above the sum insured threshold refused until three signatories are chosen, the file Renewal_QuickProposal_&lt;reference&gt;_&lt;MMDDYYYY&gt;.pdf attached, the CCM success message with the CCM transaction reference, an invalid recipient refused with nothing sent.</t>
         </is>
       </c>
     </row>
@@ -6872,7 +6872,7 @@
       </c>
       <c r="F78" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G78" s="12" t="inlineStr">
@@ -6882,7 +6882,7 @@
       </c>
       <c r="H78" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI sends the proposal through CCM with six delivery statuses; the system sends by its own e-mail with a send log.</t>
+          <t>Proposal tests: Generate Proposal Slip only for For Proposal, a Full Proposal of a non-package account above the sum insured threshold refused until three signatories are chosen, the file Renewal_QuickProposal_&lt;reference&gt;_&lt;MMDDYYYY&gt;.pdf attached, the CCM success message with the CCM transaction reference, an invalid recipient refused with nothing sent.</t>
         </is>
       </c>
     </row>
@@ -6914,7 +6914,7 @@
       </c>
       <c r="F79" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G79" s="12" t="inlineStr">
@@ -6924,7 +6924,7 @@
       </c>
       <c r="H79" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI sends For Quotation to TSU with Team Lead approval, TSU officer, comparative table and proposal; ours sends For Proposal to the non-package proposal request (TSU) and For Quotation to the package quotation: the two words are swapped (sheet 8).</t>
+          <t>TSU request tests: Pending Team Lead Approval with the Team Lead notified, the TSU officer chosen on approval, quotations recorded per insurer, a second request for the same account refused.</t>
         </is>
       </c>
     </row>
@@ -6956,7 +6956,7 @@
       </c>
       <c r="F80" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G80" s="12" t="inlineStr">
@@ -6966,7 +6966,7 @@
       </c>
       <c r="H80" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI records the client's answer to the proposal (Pending, Accepted, Rejected, Request for Revision; rejected becomes Not for Renewal, Lost Business); ours closes the renewal as Lost when the quotation is declined.</t>
+          <t>Client acceptance tests: a proposal rejected by the client sets Not for Renewal with the reason Lost Business, a revised proposal returns the status to Pending Client Response.</t>
         </is>
       </c>
     </row>
@@ -7124,7 +7124,7 @@
       </c>
       <c r="F84" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G84" s="12" t="inlineStr">
@@ -7134,7 +7134,7 @@
       </c>
       <c r="H84" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours lets the user choose First or Second Notice; BDOI determines the notice (Annex M: 75 and 45 days before expiry), names the file &lt;Product&gt;_RA_&lt;Notice#&gt;_&lt;Ref&gt;_&lt;Date&gt;.pdf and uses four approved RA templates by line (Annex L).</t>
+          <t>Renewal Advice tests: the file &lt;Product&gt;_RA_&lt;Notice&gt;_&lt;Reference&gt;_&lt;MMDDYYYY&gt;.pdf attached, the user's confirmation when generated within 20 days of expiry, no disposition change after generation, the function refused without the permission; sending through CCM or protected e-mail with a password e-mail per account, failed sendings listed with the error and resent.</t>
         </is>
       </c>
     </row>
@@ -7166,7 +7166,7 @@
       </c>
       <c r="F85" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G85" s="12" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="H85" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI sends the RA through CCM with delivery statuses; the system sends a protected e-mail and the password in a separate e-mail.</t>
+          <t>Renewal Advice tests: the file &lt;Product&gt;_RA_&lt;Notice&gt;_&lt;Reference&gt;_&lt;MMDDYYYY&gt;.pdf attached, the user's confirmation when generated within 20 days of expiry, no disposition change after generation, the function refused without the permission; sending through CCM or protected e-mail with a password e-mail per account, failed sendings listed with the error and resent.</t>
         </is>
       </c>
     </row>
@@ -7208,7 +7208,7 @@
       </c>
       <c r="F86" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G86" s="12" t="inlineStr">
@@ -7218,7 +7218,7 @@
       </c>
       <c r="H86" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours has the RA, NAL, Not for Renewal Letter, NRNS reminder and non-acceptance letter; FFY reminder and SFU letters appear only for submitted policies (FR-RN-090). Eligibility and schedules differ (Annex M, sheet 8).</t>
+          <t>Client letter tests: no closing letter during a confirmed hold cover, No Advice Letter and Non-Renewal Letter excluding each other, the file &lt;Product&gt;_NRL_&lt;Reference&gt;_&lt;MMDDYYYY&gt;.pdf attached, a resend keeping the original letter with the resend in the audit log.</t>
         </is>
       </c>
     </row>
@@ -7250,7 +7250,7 @@
       </c>
       <c r="F87" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G87" s="12" t="inlineStr">
@@ -7260,7 +7260,7 @@
       </c>
       <c r="H87" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Same generation, storage, preview and resend; BDOI fixes the file name &lt;Product&gt;_&lt;Letter Type&gt;_&lt;Ref&gt;_&lt;Date&gt;.pdf and the messages; channel CCM against the system e-mail.</t>
+          <t>Client letter tests: no closing letter during a confirmed hold cover, No Advice Letter and Non-Renewal Letter excluding each other, the file &lt;Product&gt;_NRL_&lt;Reference&gt;_&lt;MMDDYYYY&gt;.pdf attached, a resend keeping the original letter with the resend in the audit log.</t>
         </is>
       </c>
     </row>
@@ -7292,7 +7292,7 @@
       </c>
       <c r="F88" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G88" s="12" t="inlineStr">
@@ -7302,7 +7302,7 @@
       </c>
       <c r="H88" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI's password: individuals - first three letters of the first and last names in capitals; corporate - eight random characters (one lower case, one upper case, one special, five digits). the system generates a random 12-character password, pending the convention (Q07).</t>
+          <t>Password convention tests: JUADEL for Juan Dela Cruz and LIONG for Li Ong, eight characters with a lower-case letter, an upper-case letter, a special character and five digits for a corporate client, the PDF not opened without the password.</t>
         </is>
       </c>
     </row>
@@ -7334,7 +7334,7 @@
       </c>
       <c r="F89" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G89" s="12" t="inlineStr">
@@ -7344,7 +7344,7 @@
       </c>
       <c r="H89" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours records the acceptance with its method and evidence; BDOI uses statuses (Pending, Accepted, Rejected, Request for Revision, Not Applicable), exempts CBG Home and FFY accounts (they go to For Billing Generation) and sends the Non-Renewal Letter on rejection.</t>
+          <t>Client acceptance tests: an acceptance by e-mail with the client's e-mail attached sets Accepted and moves the account on; an acceptance with a financial impact refused without evidence.</t>
         </is>
       </c>
     </row>
@@ -7376,7 +7376,7 @@
       </c>
       <c r="F90" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G90" s="12" t="inlineStr">
@@ -7386,7 +7386,7 @@
       </c>
       <c r="H90" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI adds a second approval after acceptance (Submitted for Approval), auto-submits CBG Motor on payment and requires the payment confirmation for Non-CBG; ours moves the accepted account to placement and booking once the payment rules are met, without a second approval.</t>
+          <t>Approval tests: an approved Non-CBG account without the payment confirmation status shows Please select the client's payment confirmation status., a rejected account Returned Account in its officer's queue with the resubmission date and time.</t>
         </is>
       </c>
     </row>
@@ -7418,7 +7418,7 @@
       </c>
       <c r="F91" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G91" s="12" t="inlineStr">
@@ -7428,7 +7428,7 @@
       </c>
       <c r="H91" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Scheduled CLPC billing (CBG Home daily at 10 days before expiry; FFY Motor on the 10th and 25th), Built-in and Non-Built-in files; the system creates the CLPC billing batch on demand and the file is sent outside the system.</t>
+          <t>CLPC billing file tests: the daily CBG Home file of the accounts For Billing Generation expiring 10 days later attached to each account, the manual file with a period of at most 31 days and From Date not after To Date, the file sent to the recipients with its delivery status on the billing record.</t>
         </is>
       </c>
     </row>
@@ -7460,7 +7460,7 @@
       </c>
       <c r="F92" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G92" s="12" t="inlineStr">
@@ -7470,7 +7470,7 @@
       </c>
       <c r="H92" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Manual billing file with a From / To window of at most 31 days.</t>
+          <t>CLPC billing file tests: the daily CBG Home file of the accounts For Billing Generation expiring 10 days later attached to each account, the manual file with a period of at most 31 days and From Date not after To Date, the file sent to the recipients with its delivery status on the billing record.</t>
         </is>
       </c>
     </row>
@@ -7502,7 +7502,7 @@
       </c>
       <c r="F93" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G93" s="12" t="inlineStr">
@@ -7512,7 +7512,7 @@
       </c>
       <c r="H93" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Sending the billing file with delivery status (Annex S e-mail).</t>
+          <t>CLPC billing file tests: the daily CBG Home file of the accounts For Billing Generation expiring 10 days later attached to each account, the manual file with a period of at most 31 days and From Date not after To Date, the file sent to the recipients with its delivery status on the billing record.</t>
         </is>
       </c>
     </row>
@@ -7544,7 +7544,7 @@
       </c>
       <c r="F94" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G94" s="12" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="H94" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours reads the payment status of the payment gate; BDOI names Paid, Partially Paid and Unpaid from the outstanding balance.</t>
+          <t>Payment status tests: Paid, Partially Paid and Unpaid from the payments applied in Cashiering against the gross premium; a CBG account Paid moves to Submitted for Placement without a user action.</t>
         </is>
       </c>
     </row>
@@ -7586,7 +7586,7 @@
       </c>
       <c r="F95" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G95" s="12" t="inlineStr">
@@ -7596,7 +7596,7 @@
       </c>
       <c r="H95" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI moves a paid CBG renewal to Submitted for Placement automatically; ours moves an accepted renewal to placement and booking once the payment rules are met and leaves the placement itself to the user.</t>
+          <t>Payment status tests: Paid, Partially Paid and Unpaid from the payments applied in Cashiering against the gross premium; a CBG account Paid moves to Submitted for Placement without a user action.</t>
         </is>
       </c>
     </row>
@@ -7638,7 +7638,7 @@
       </c>
       <c r="H96" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: The Submitted for Placement list; ours refers to the New Business placement.</t>
+          <t>Placement tests: one slip per insurer of each account and none For Booking Only, one placement file per insurer for packaged accounts with each co-insurer's share, Is Generated Placement with the date and user, MFT upload for enrolled insurers and Upload Failed shown, CCM sending to the Insurer Maintenance recipients with an invalid address refused and the account then For Booking, TAT in business days from the next day after the cut-off with With Issue and the resolution date.</t>
         </is>
       </c>
     </row>
@@ -7670,7 +7670,7 @@
       </c>
       <c r="F97" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G97" s="12" t="inlineStr">
@@ -7680,7 +7680,7 @@
       </c>
       <c r="H97" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: One slip per insurer per account and a consolidated Excel file per insurer for packaged accounts, excluding For Booking Only; the system makes one slip per insurer branch.</t>
+          <t>Placement tests: one slip per insurer of each account and none For Booking Only, one placement file per insurer for packaged accounts with each co-insurer's share, Is Generated Placement with the date and user, MFT upload for enrolled insurers and Upload Failed shown, CCM sending to the Insurer Maintenance recipients with an invalid address refused and the account then For Booking, TAT in business days from the next day after the cut-off with With Issue and the resolution date.</t>
         </is>
       </c>
     </row>
@@ -7712,7 +7712,7 @@
       </c>
       <c r="F98" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G98" s="12" t="inlineStr">
@@ -7722,7 +7722,7 @@
       </c>
       <c r="H98" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Placement slip file name and stored details; BDOI's example name carries two product codes.</t>
+          <t>Placement tests: one slip per insurer of each account and none For Booking Only, one placement file per insurer for packaged accounts with each co-insurer's share, Is Generated Placement with the date and user, MFT upload for enrolled insurers and Upload Failed shown, CCM sending to the Insurer Maintenance recipients with an invalid address refused and the account then For Booking, TAT in business days from the next day after the cut-off with With Issue and the resolution date.</t>
         </is>
       </c>
     </row>
@@ -7754,7 +7754,7 @@
       </c>
       <c r="F99" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G99" s="12" t="inlineStr">
@@ -7764,7 +7764,7 @@
       </c>
       <c r="H99" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Consolidated placement file per insurer; BDOI's example is a.pdf with a reference number although the file is an.xlsx per insurer.</t>
+          <t>Placement tests: one slip per insurer of each account and none For Booking Only, one placement file per insurer for packaged accounts with each co-insurer's share, Is Generated Placement with the date and user, MFT upload for enrolled insurers and Upload Failed shown, CCM sending to the Insurer Maintenance recipients with an invalid address refused and the account then For Booking, TAT in business days from the next day after the cut-off with With Issue and the resolution date.</t>
         </is>
       </c>
     </row>
@@ -7796,7 +7796,7 @@
       </c>
       <c r="F100" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G100" s="12" t="inlineStr">
@@ -7806,7 +7806,7 @@
       </c>
       <c r="H100" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Automatic upload of placement files through MFT; ours has no file-transfer channel with insurers (on hold).</t>
+          <t>Placement sending tests: MFT upload for the insurers tagged MFT Enrolled with Upload Failed shown and the others waiting for e-mail, CCM sending to the Insurer Maintenance recipients changeable before sending with an invalid address refused, the account For Booking after a successful sending, the TAT counted from the next business day after the cut-off hour and Beyond TAT from the fourth business day, With Issue measured to the resolution date and a resolution date before the submission refused.</t>
         </is>
       </c>
     </row>
@@ -7838,7 +7838,7 @@
       </c>
       <c r="F101" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G101" s="12" t="inlineStr">
@@ -7848,7 +7848,7 @@
       </c>
       <c r="H101" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Sending placement files through CCM with recipients from Insurer Maintenance; the system sends the slips by e-mail.</t>
+          <t>Placement sending tests: MFT upload for the insurers tagged MFT Enrolled with Upload Failed shown and the others waiting for e-mail, CCM sending to the Insurer Maintenance recipients changeable before sending with an invalid address refused, the account For Booking after a successful sending, the TAT counted from the next business day after the cut-off hour and Beyond TAT from the fourth business day, With Issue measured to the resolution date and a resolution date before the submission refused.</t>
         </is>
       </c>
     </row>
@@ -7880,7 +7880,7 @@
       </c>
       <c r="F102" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G102" s="12" t="inlineStr">
@@ -7890,7 +7890,7 @@
       </c>
       <c r="H102" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours sets a reply due date for insurer batches and alerts when overdue; BDOI measures placement TAT in business days (3 packaged, 10 non-package, 3PM cut-off) with a With Issue tag and resolution date.</t>
+          <t>Placement sending tests: MFT upload for the insurers tagged MFT Enrolled with Upload Failed shown and the others waiting for e-mail, CCM sending to the Insurer Maintenance recipients changeable before sending with an invalid address refused, the account For Booking after a successful sending, the TAT counted from the next business day after the cut-off hour and Beyond TAT from the fourth business day, With Issue measured to the resolution date and a resolution date before the submission refused.</t>
         </is>
       </c>
     </row>
@@ -7922,7 +7922,7 @@
       </c>
       <c r="F103" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G103" s="12" t="inlineStr">
@@ -7932,7 +7932,7 @@
       </c>
       <c r="H103" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Placement response by upload or MFT, matched on the renewal reference; ours covers the insurer's renewal response before the RA, not the placement response.</t>
+          <t>Placement response tests: responses matched on the renewal reference with the unmatched listed, Approved with the response date and remarks, Rejected with its reason and Rejected Placement then return to Marketing or cancellation, one summary row per file latest first, the record-level view filtered by Matched and Unmatched and by Approved and Rejected.</t>
         </is>
       </c>
     </row>
@@ -7964,7 +7964,7 @@
       </c>
       <c r="F104" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G104" s="12" t="inlineStr">
@@ -7974,7 +7974,7 @@
       </c>
       <c r="H104" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI books the account and locks it when the insurer approves the placement; ours keeps booking a user action (Walkthrough addendum p.4).</t>
+          <t>Placement response tests: responses matched on the renewal reference with the unmatched listed, Approved with the response date and remarks, Rejected with its reason and Rejected Placement then return to Marketing or cancellation, one summary row per file latest first, the record-level view filtered by Matched and Unmatched and by Approved and Rejected.</t>
         </is>
       </c>
     </row>
@@ -8006,7 +8006,7 @@
       </c>
       <c r="F105" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G105" s="12" t="inlineStr">
@@ -8016,7 +8016,7 @@
       </c>
       <c r="H105" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Rejected placement with seven reasons, status Rejected Placement, return to Marketing or cancel the placement.</t>
+          <t>Placement response tests: responses matched on the renewal reference with the unmatched listed, Approved with the response date and remarks, Rejected with its reason and Rejected Placement then return to Marketing or cancellation, one summary row per file latest first, the record-level view filtered by Matched and Unmatched and by Approved and Rejected.</t>
         </is>
       </c>
     </row>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="F106" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G106" s="12" t="inlineStr">
@@ -8058,7 +8058,7 @@
       </c>
       <c r="H106" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Summary of the placement response files.</t>
+          <t>Placement response tests: responses matched on the renewal reference with the unmatched listed, Approved with the response date and remarks, Rejected with its reason and Rejected Placement then return to Marketing or cancellation, one summary row per file latest first, the record-level view filtered by Matched and Unmatched and by Approved and Rejected.</t>
         </is>
       </c>
     </row>
@@ -8090,7 +8090,7 @@
       </c>
       <c r="F107" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G107" s="12" t="inlineStr">
@@ -8100,7 +8100,7 @@
       </c>
       <c r="H107" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Record-level view of the placement responses.</t>
+          <t>Placement response tests: responses matched on the renewal reference with the unmatched listed, Approved with the response date and remarks, Rejected with its reason and Rejected Placement then return to Marketing or cancellation, one summary row per file latest first, the record-level view filtered by Matched and Unmatched and by Approved and Rejected.</t>
         </is>
       </c>
     </row>
@@ -8132,7 +8132,7 @@
       </c>
       <c r="F108" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G108" s="12" t="inlineStr">
@@ -8142,7 +8142,7 @@
       </c>
       <c r="H108" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours returns from processing to the AO or Team Lead with five return reasons; BDOI returns from Submitted for Placement and Rejected Placement with status Returned - Renewal and 39 reasons (Annex V).</t>
+          <t>Return to Marketing tests: the account back in the Account Officer's list with the Returned flag and the reason, a return without reason refused.</t>
         </is>
       </c>
     </row>
@@ -8174,7 +8174,7 @@
       </c>
       <c r="F109" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G109" s="12" t="inlineStr">
@@ -8184,7 +8184,7 @@
       </c>
       <c r="H109" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Insurance Advice for mortgaged accounts when the placement is sent, versioned on change; the system generates it for mortgaged accounts on the event set by a parameter (policy issue by default).</t>
+          <t>Insurance Advice tests: IA_&lt;reference&gt;_&lt;MMDDYYYY&gt;.pdf generated for a mortgaged account when the placement is sent and versioned on a change, none for an account without mortgage, Send Insurance Advice disabled when a selected account has none, sending through CCM.</t>
         </is>
       </c>
     </row>
@@ -8216,7 +8216,7 @@
       </c>
       <c r="F110" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G110" s="12" t="inlineStr">
@@ -8226,7 +8226,7 @@
       </c>
       <c r="H110" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Sending the Insurance Advice through CCM with CC recipients; the system sends by e-mail.</t>
+          <t>Insurance Advice tests: IA_&lt;reference&gt;_&lt;MMDDYYYY&gt;.pdf generated for a mortgaged account when the placement is sent and versioned on a change, none for an account without mortgage, Send Insurance Advice disabled when a selected account has none, sending through CCM.</t>
         </is>
       </c>
     </row>
@@ -8258,7 +8258,7 @@
       </c>
       <c r="F111" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G111" s="12" t="inlineStr">
@@ -8268,7 +8268,7 @@
       </c>
       <c r="H111" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: E-policy processing in the Renewal FRS; ours refers to New Business issuance.</t>
+          <t>E-policy tests: the policy number of the summary file updating the matching account, a ZIP document not in the summary refused and a matched one attached, one summary row per received file with its type and status, the record-level matching view, sending through CCM excluding accounts without a valid e-mail or not For E-Policy Sending, an e-policy number held by another active account listed in the exception report.</t>
         </is>
       </c>
     </row>
@@ -8300,7 +8300,7 @@
       </c>
       <c r="F112" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G112" s="12" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="H112" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: One summary text file and one ZIP per upload, or MFT; the system uploads policy PDFs matched on the account reference in the file name.</t>
+          <t>E-policy tests: the policy number of the summary file updating the matching account, a ZIP document not in the summary refused and a matched one attached, one summary row per received file with its type and status, the record-level matching view, sending through CCM excluding accounts without a valid e-mail or not For E-Policy Sending, an e-policy number held by another active account listed in the exception report.</t>
         </is>
       </c>
     </row>
@@ -8342,7 +8342,7 @@
       </c>
       <c r="F113" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G113" s="12" t="inlineStr">
@@ -8352,7 +8352,7 @@
       </c>
       <c r="H113" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Receipt summary of e-policy files.</t>
+          <t>E-policy tests: the policy number of the summary file updating the matching account, a ZIP document not in the summary refused and a matched one attached, one summary row per received file with its type and status, the record-level matching view, sending through CCM excluding accounts without a valid e-mail or not For E-Policy Sending, an e-policy number held by another active account listed in the exception report.</t>
         </is>
       </c>
     </row>
@@ -8384,7 +8384,7 @@
       </c>
       <c r="F114" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G114" s="12" t="inlineStr">
@@ -8394,7 +8394,7 @@
       </c>
       <c r="H114" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Record-level view of e-policy files.</t>
+          <t>E-policy tests: the policy number of the summary file updating the matching account, a ZIP document not in the summary refused and a matched one attached, one summary row per received file with its type and status, the record-level matching view, sending through CCM excluding accounts without a valid e-mail or not For E-Policy Sending, an e-policy number held by another active account listed in the exception report.</t>
         </is>
       </c>
     </row>
@@ -8426,7 +8426,7 @@
       </c>
       <c r="F115" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G115" s="12" t="inlineStr">
@@ -8436,7 +8436,7 @@
       </c>
       <c r="H115" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Bulk e-policy sending through CCM with eligibility checks; the system sends encrypted e-policies by e-mail.</t>
+          <t>E-policy tests: the policy number of the summary file updating the matching account, a ZIP document not in the summary refused and a matched one attached, one summary row per received file with its type and status, the record-level matching view, sending through CCM excluding accounts without a valid e-mail or not For E-Policy Sending, an e-policy number held by another active account listed in the exception report.</t>
         </is>
       </c>
     </row>
@@ -8468,7 +8468,7 @@
       </c>
       <c r="F116" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G116" s="12" t="inlineStr">
@@ -8478,7 +8478,7 @@
       </c>
       <c r="H116" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Batch upload of e-policy numbers with a duplicate check across active accounts and an exception report.</t>
+          <t>E-policy tests: the policy number of the summary file updating the matching account, a ZIP document not in the summary refused and a matched one attached, one summary row per received file with its type and status, the record-level matching view, sending through CCM excluding accounts without a valid e-mail or not For E-Policy Sending, an e-policy number held by another active account listed in the exception report.</t>
         </is>
       </c>
     </row>
@@ -8594,7 +8594,7 @@
       </c>
       <c r="F119" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G119" s="12" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="H119" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI defaults 30 days (Non-CBG) and 90 days (CBG), and 30 (CBG Home) or 60 (CBG Motor) for transferred accounts; ours offers 30 or 60 days, 30 by default.</t>
+          <t>Hold cover tests: 30 days Non-CBG, 90 days CBG and 60 days for a CBG Motor account after an insurer's rejection, one request per co-insurer after the client's confirmation, a second request refused until the first is cancelled, extensions of 15 or 30 days from 7 days before the end, the CBG files per insurer 75 days before expiry, the 30-day CBG Home extension on the 15th, MFT upload for enrolled insurers and e-mail with the document for the others.</t>
         </is>
       </c>
     </row>
@@ -8636,7 +8636,7 @@
       </c>
       <c r="F120" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G120" s="12" t="inlineStr">
@@ -8646,7 +8646,7 @@
       </c>
       <c r="H120" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI generates the Non-CBG request automatically after the client's confirmation, one per co-insurer; ours sends it when the user requests it.</t>
+          <t>Hold cover tests: 30 days Non-CBG, 90 days CBG and 60 days for a CBG Motor account after an insurer's rejection, one request per co-insurer after the client's confirmation, a second request refused until the first is cancelled, extensions of 15 or 30 days from 7 days before the end, the CBG files per insurer 75 days before expiry, the 30-day CBG Home extension on the 15th, MFT upload for enrolled insurers and e-mail with the document for the others.</t>
         </is>
       </c>
     </row>
@@ -8678,7 +8678,7 @@
       </c>
       <c r="F121" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G121" s="12" t="inlineStr">
@@ -8688,7 +8688,7 @@
       </c>
       <c r="H121" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Extension of 15 or 30 days from 7 days before the hold cover ends; ours allows a new request only after the previous hold cover expired or was cancelled.</t>
+          <t>Hold cover tests: 30 days Non-CBG, 90 days CBG and 60 days for a CBG Motor account after an insurer's rejection, one request per co-insurer after the client's confirmation, a second request refused until the first is cancelled, extensions of 15 or 30 days from 7 days before the end, the CBG files per insurer 75 days before expiry, the 30-day CBG Home extension on the 15th, MFT upload for enrolled insurers and e-mail with the document for the others.</t>
         </is>
       </c>
     </row>
@@ -8720,7 +8720,7 @@
       </c>
       <c r="F122" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G122" s="12" t="inlineStr">
@@ -8730,7 +8730,7 @@
       </c>
       <c r="H122" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Automatic CBG requests for Clean accounts 75 days before expiry, one Excel file per insurer.</t>
+          <t>Hold cover tests: 30 days Non-CBG, 90 days CBG and 60 days for a CBG Motor account after an insurer's rejection, one request per co-insurer after the client's confirmation, a second request refused until the first is cancelled, extensions of 15 or 30 days from 7 days before the end, the CBG files per insurer 75 days before expiry, the 30-day CBG Home extension on the 15th, MFT upload for enrolled insurers and e-mail with the document for the others.</t>
         </is>
       </c>
     </row>
@@ -8762,7 +8762,7 @@
       </c>
       <c r="F123" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G123" s="12" t="inlineStr">
@@ -8772,7 +8772,7 @@
       </c>
       <c r="H123" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Automatic 30-day extension for expired and unbooked CBG Home accounts on the 15th of each month.</t>
+          <t>Hold cover tests: 30 days Non-CBG, 90 days CBG and 60 days for a CBG Motor account after an insurer's rejection, one request per co-insurer after the client's confirmation, a second request refused until the first is cancelled, extensions of 15 or 30 days from 7 days before the end, the CBG files per insurer 75 days before expiry, the 30-day CBG Home extension on the 15th, MFT upload for enrolled insurers and e-mail with the document for the others.</t>
         </is>
       </c>
     </row>
@@ -8804,7 +8804,7 @@
       </c>
       <c r="F124" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G124" s="12" t="inlineStr">
@@ -8814,7 +8814,7 @@
       </c>
       <c r="H124" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours e-mails the request from the hold cover template; BDOI uploads to MFT for enrolled insurers and e-mails the others.</t>
+          <t>Hold cover tests: 30 days Non-CBG, 90 days CBG and 60 days for a CBG Motor account after an insurer's rejection, one request per co-insurer after the client's confirmation, a second request refused until the first is cancelled, extensions of 15 or 30 days from 7 days before the end, the CBG files per insurer 75 days before expiry, the 30-day CBG Home extension on the 15th, MFT upload for enrolled insurers and e-mail with the document for the others.</t>
         </is>
       </c>
     </row>
@@ -8846,7 +8846,7 @@
       </c>
       <c r="F125" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G125" s="12" t="inlineStr">
@@ -8856,7 +8856,7 @@
       </c>
       <c r="H125" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours records the confirmation by hand; BDOI also uploads response files (or MFT) matched on the reference number.</t>
+          <t>Hold cover response tests: matched by the reference number, Approved confirming the hold cover with the effective expiry at its end, Rejected returning the account with the insurer's remarks, one summary row per file latest first, the record-level view filtered by Matched and Unmatched and by Approved and Rejected.</t>
         </is>
       </c>
     </row>
@@ -8888,7 +8888,7 @@
       </c>
       <c r="F126" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G126" s="12" t="inlineStr">
@@ -8898,7 +8898,7 @@
       </c>
       <c r="H126" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Approved and Rejected responses update the hold cover; a rejection returns the account to the user.</t>
+          <t>Hold cover response tests: matched by the reference number, Approved confirming the hold cover with the effective expiry at its end, Rejected returning the account with the insurer's remarks, one summary row per file latest first, the record-level view filtered by Matched and Unmatched and by Approved and Rejected.</t>
         </is>
       </c>
     </row>
@@ -8930,7 +8930,7 @@
       </c>
       <c r="F127" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G127" s="12" t="inlineStr">
@@ -8940,7 +8940,7 @@
       </c>
       <c r="H127" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Summary of hold cover response files.</t>
+          <t>Hold cover response tests: matched by the reference number, Approved confirming the hold cover with the effective expiry at its end, Rejected returning the account with the insurer's remarks, one summary row per file latest first, the record-level view filtered by Matched and Unmatched and by Approved and Rejected.</t>
         </is>
       </c>
     </row>
@@ -8972,7 +8972,7 @@
       </c>
       <c r="F128" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G128" s="12" t="inlineStr">
@@ -8982,7 +8982,7 @@
       </c>
       <c r="H128" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Record-level view of hold cover responses.</t>
+          <t>Hold cover response tests: matched by the reference number, Approved confirming the hold cover with the effective expiry at its end, Rejected returning the account with the insurer's remarks, one summary row per file latest first, the record-level view filtered by Matched and Unmatched and by Approved and Rejected.</t>
         </is>
       </c>
     </row>
@@ -9024,7 +9024,7 @@
       </c>
       <c r="H129" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Manual update of the response, dates, remarks and documents; remarks mandatory on rejection.</t>
+          <t>Hold cover response tests: matched by the reference number, Approved confirming the hold cover with the effective expiry at its end, Rejected returning the account with the insurer's remarks, one summary row per file latest first, the record-level view filtered by Matched and Unmatched and by Approved and Rejected.</t>
         </is>
       </c>
     </row>
@@ -9056,7 +9056,7 @@
       </c>
       <c r="F130" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G130" s="12" t="inlineStr">
@@ -9066,7 +9066,7 @@
       </c>
       <c r="H130" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours keeps a list of non-renewable risk codes; BDOI keeps every risk code with a Renewable / Non-Renewable indicator, read-only to other users.</t>
+          <t>Risk Code Maintenance tests: read only without the maintenance function, a change in force only once another user authorises it, the list with description, line, indicator, status and created and updated by and on, Duplicate entry detected. The risk code already exists in the list., retroactive dates refused, Record successfully updated. with the old and new values in the log, a Non-Renewable risk code giving Not for Renewal with the reason at the next generation.</t>
         </is>
       </c>
     </row>
@@ -9098,7 +9098,7 @@
       </c>
       <c r="F131" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G131" s="12" t="inlineStr">
@@ -9108,7 +9108,7 @@
       </c>
       <c r="H131" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: View with description, line, indicator, status and the audit fields.</t>
+          <t>Risk Code Maintenance tests: read only without the maintenance function, a change in force only once another user authorises it, the list with description, line, indicator, status and created and updated by and on, Duplicate entry detected. The risk code already exists in the list., retroactive dates refused, Record successfully updated. with the old and new values in the log, a Non-Renewable risk code giving Not for Renewal with the reason at the next generation.</t>
         </is>
       </c>
     </row>
@@ -9140,7 +9140,7 @@
       </c>
       <c r="F132" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G132" s="12" t="inlineStr">
@@ -9150,7 +9150,7 @@
       </c>
       <c r="H132" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours has effective-from and effective-to dates and a checker; BDOI blocks retroactive dates and duplicates with its messages and records the reason "Non-Renewable Risk Code" (ours "Non-renewable Accounts").</t>
+          <t>Risk Code Maintenance tests: read only without the maintenance function, a change in force only once another user authorises it, the list with description, line, indicator, status and created and updated by and on, Duplicate entry detected. The risk code already exists in the list., retroactive dates refused, Record successfully updated. with the old and new values in the log, a Non-Renewable risk code giving Not for Renewal with the reason at the next generation.</t>
         </is>
       </c>
     </row>
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F133" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G133" s="12" t="inlineStr">
@@ -9192,7 +9192,7 @@
       </c>
       <c r="H133" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Update of a risk code with the same validations and log.</t>
+          <t>Risk Code Maintenance tests: read only without the maintenance function, a change in force only once another user authorises it, the list with description, line, indicator, status and created and updated by and on, Duplicate entry detected. The risk code already exists in the list., retroactive dates refused, Record successfully updated. with the old and new values in the log, a Non-Renewable risk code giving Not for Renewal with the reason at the next generation.</t>
         </is>
       </c>
     </row>
@@ -9224,7 +9224,7 @@
       </c>
       <c r="F134" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G134" s="12" t="inlineStr">
@@ -9234,7 +9234,7 @@
       </c>
       <c r="H134" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Both flag KYC due without blocking; BDOI makes the criteria configurable (schedules, expiry, bank / non-bank, product, regulation), ours reads the client's KYC review date.</t>
+          <t>KYC tests: the KYC due flag without a change of classification, Completed recorded with the history of earlier statuses, user and time, the KYC Monitoring dashboard opening the accounts due.</t>
         </is>
       </c>
     </row>
@@ -9266,7 +9266,7 @@
       </c>
       <c r="F135" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G135" s="12" t="inlineStr">
@@ -9276,7 +9276,7 @@
       </c>
       <c r="H135" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: KYC statuses (Due, Upcoming, Not Required, Pending Follow-Up, Completed) with history and review activities.</t>
+          <t>KYC tests: the KYC due flag without a change of classification, Completed recorded with the history of earlier statuses, user and time, the KYC Monitoring dashboard opening the accounts due.</t>
         </is>
       </c>
     </row>
@@ -9308,7 +9308,7 @@
       </c>
       <c r="F136" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G136" s="12" t="inlineStr">
@@ -9318,7 +9318,7 @@
       </c>
       <c r="H136" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: KYC monitoring dashboard with drill-down.</t>
+          <t>KYC tests: the KYC due flag without a change of classification, Completed recorded with the history of earlier statuses, user and time, the KYC Monitoring dashboard opening the accounts due.</t>
         </is>
       </c>
     </row>
@@ -9392,7 +9392,7 @@
       </c>
       <c r="F138" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G138" s="12" t="inlineStr">
@@ -9402,7 +9402,7 @@
       </c>
       <c r="H138" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: BDOI keeps a list of RMU Account Officer codes and derives RMU from the AO code of the loan; ours takes RMU from the LAMD report.</t>
+          <t>RMU Account Maintenance tests: a second active record of the same Account Officer code refused, a LAMD loan of an RMU Account Officer identified as RMU.</t>
         </is>
       </c>
     </row>
@@ -9434,7 +9434,7 @@
       </c>
       <c r="F139" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G139" s="12" t="inlineStr">
@@ -9444,7 +9444,7 @@
       </c>
       <c r="H139" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Renewal annual budget maintenance; the system has production targets per sales unit in New Business.</t>
+          <t>Annual Renewal Budget tests: no menu without the budget function, the annual total equal to the twelve months, the upload creating or updating the records, negative amounts and a Corporate budget without team refused, Budget Inquiry by fiscal year, segment and hierarchy, the history of each monthly change with user and time.</t>
         </is>
       </c>
     </row>
@@ -9476,7 +9476,7 @@
       </c>
       <c r="F140" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G140" s="12" t="inlineStr">
@@ -9486,7 +9486,7 @@
       </c>
       <c r="H140" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Monthly new, renewal and organic budgets per unit, segment, region, team and officer with annual totals.</t>
+          <t>Annual Renewal Budget tests: no menu without the budget function, the annual total equal to the twelve months, the upload creating or updating the records, negative amounts and a Corporate budget without team refused, Budget Inquiry by fiscal year, segment and hierarchy, the history of each monthly change with user and time.</t>
         </is>
       </c>
     </row>
@@ -9518,7 +9518,7 @@
       </c>
       <c r="F141" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G141" s="12" t="inlineStr">
@@ -9528,7 +9528,7 @@
       </c>
       <c r="H141" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Budget upload with a template.</t>
+          <t>Annual Renewal Budget tests: no menu without the budget function, the annual total equal to the twelve months, the upload creating or updating the records, negative amounts and a Corporate budget without team refused, Budget Inquiry by fiscal year, segment and hierarchy, the history of each monthly change with user and time.</t>
         </is>
       </c>
     </row>
@@ -9560,7 +9560,7 @@
       </c>
       <c r="F142" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G142" s="12" t="inlineStr">
@@ -9570,7 +9570,7 @@
       </c>
       <c r="H142" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Budget validations (mandatory fiscal year and segment, region or team by segment, no negative values).</t>
+          <t>Annual Renewal Budget tests: no menu without the budget function, the annual total equal to the twelve months, the upload creating or updating the records, negative amounts and a Corporate budget without team refused, Budget Inquiry by fiscal year, segment and hierarchy, the history of each monthly change with user and time.</t>
         </is>
       </c>
     </row>
@@ -9602,7 +9602,7 @@
       </c>
       <c r="F143" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G143" s="12" t="inlineStr">
@@ -9612,7 +9612,7 @@
       </c>
       <c r="H143" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Budget inquiry screen.</t>
+          <t>Annual Renewal Budget tests: no menu without the budget function, the annual total equal to the twelve months, the upload creating or updating the records, negative amounts and a Corporate budget without team refused, Budget Inquiry by fiscal year, segment and hierarchy, the history of each monthly change with user and time.</t>
         </is>
       </c>
     </row>
@@ -9644,7 +9644,7 @@
       </c>
       <c r="F144" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G144" s="12" t="inlineStr">
@@ -9654,7 +9654,7 @@
       </c>
       <c r="H144" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Budget history with previous and updated values.</t>
+          <t>Annual Renewal Budget tests: no menu without the budget function, the annual total equal to the twelve months, the upload creating or updating the records, negative amounts and a Corporate budget without team refused, Budget Inquiry by fiscal year, segment and hierarchy, the history of each monthly change with user and time.</t>
         </is>
       </c>
     </row>
@@ -9686,7 +9686,7 @@
       </c>
       <c r="F145" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G145" s="12" t="inlineStr">
@@ -9696,7 +9696,7 @@
       </c>
       <c r="H145" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours keeps an unchangeable history and audit per renewal with decision and sanitation reports; BDOI adds an Audit Logs menu with old and new values and export.</t>
+          <t>Audit Logs tests: the extraction, sanitation, classification, disposition, posting, insurer disposition and later steps of a renewed account listed with old and new values, no screen to change or delete an entry, CSV and Excel export.</t>
         </is>
       </c>
     </row>
@@ -9770,7 +9770,7 @@
       </c>
       <c r="F147" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G147" s="12" t="inlineStr">
@@ -9780,7 +9780,7 @@
       </c>
       <c r="H147" s="12" t="inlineStr">
         <is>
-          <t>Comparison of BDOI's FRS with the system: Ours specifies the status report, the listing and six operational reports with their columns; BDOI lists 24 reports without layouts.</t>
+          <t>Report tests: every renewal report previewed, downloaded as Excel and PDF and printed, each user seeing only the accounts of his data scope; file names &lt;Report&gt;_&lt;MMDDYYYY&gt;.</t>
         </is>
       </c>
     </row>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="F149" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G149" s="12" t="inlineStr">
@@ -9864,7 +9864,7 @@
       </c>
       <c r="H149" s="12" t="inlineStr">
         <is>
-          <t>Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>My Dispositions tests: the Account Officer's accounts of the current and previous years without a filter, sorted by expiry both ways, the Endorsed flag with its effective date, the red Returned flag with the Team Lead's remarks leaving Returned to me once submitted again.</t>
         </is>
       </c>
     </row>
@@ -9896,7 +9896,7 @@
       </c>
       <c r="F150" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G150" s="12" t="inlineStr">
@@ -9906,7 +9906,7 @@
       </c>
       <c r="H150" s="12" t="inlineStr">
         <is>
-          <t>Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Processing Worklist tests: In Processing shows only the accounts assigned to the Processing Officer when the processing scope is set so; sorting and column filters on every column of every tab.</t>
         </is>
       </c>
     </row>
@@ -9980,7 +9980,7 @@
       </c>
       <c r="F152" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G152" s="12" t="inlineStr">
@@ -9990,7 +9990,7 @@
       </c>
       <c r="H152" s="12" t="inlineStr">
         <is>
-          <t>Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Tests of the transfer to another unit: the account leaves the sender's list for the receiving Team Lead's Transfers inbox, appears in the receiving unit's unassigned list with the Transferred flag once accepted, and returns to the sender with the decline remarks.</t>
         </is>
       </c>
     </row>
@@ -10032,7 +10032,7 @@
       </c>
       <c r="H153" s="12" t="inlineStr">
         <is>
-          <t>Available; shown in the end-to-end run of the conformance register.</t>
+          <t>Insurer disposition upload tests: the Annex H layout processed with the success messages, a missing required field refusing the file, Renew As Is setting Clean and For Renewal with premium and terms unchanged, a different expiring policy number flagged for review, Renew with surcharge setting Review, For Disposition and the financial impact.</t>
         </is>
       </c>
     </row>
@@ -10116,7 +10116,7 @@
       </c>
       <c r="H155" s="12" t="inlineStr">
         <is>
-          <t>Available; shown in the end-to-end run of the conformance register.</t>
+          <t>Renewal Update upload tests: a file with unknown references updating the other rows and listing the refused rows with their message, two files giving two results, one summary row per upload latest first, the record-level view with filter, sort and search.</t>
         </is>
       </c>
     </row>
@@ -10242,7 +10242,7 @@
       </c>
       <c r="H158" s="12" t="inlineStr">
         <is>
-          <t>Available; shown in the end-to-end run of the conformance register.</t>
+          <t>Client letter tests: no closing letter during a confirmed hold cover, No Advice Letter and Non-Renewal Letter excluding each other, the file &lt;Product&gt;_NRL_&lt;Reference&gt;_&lt;MMDDYYYY&gt;.pdf attached, a resend keeping the original letter with the resend in the audit log.</t>
         </is>
       </c>
     </row>
@@ -10400,7 +10400,7 @@
       </c>
       <c r="F162" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G162" s="12" t="inlineStr">
@@ -10410,7 +10410,7 @@
       </c>
       <c r="H162" s="12" t="inlineStr">
         <is>
-          <t>Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Renewal Status Report tests: the month with Risk Code All Except leaving out the code and showing the 34 counters, Excel and PDF with the rows of the screen, the Processing variant with the renewal processor, the Account Officer and the sum insured per cover.</t>
         </is>
       </c>
     </row>
@@ -10694,7 +10694,7 @@
       </c>
       <c r="F169" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G169" s="12" t="inlineStr">
@@ -10704,7 +10704,7 @@
       </c>
       <c r="H169" s="12" t="inlineStr">
         <is>
-          <t>Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Submitted policies tests: a CBG Motor policy handed over creates one renewal account, one hold cover request and one Renewal Advice; the Submitted Policies masterlist shows it booked once the renewal account is booked.</t>
         </is>
       </c>
     </row>
@@ -10736,7 +10736,7 @@
       </c>
       <c r="F170" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G170" s="12" t="inlineStr">
@@ -10746,7 +10746,7 @@
       </c>
       <c r="H170" s="12" t="inlineStr">
         <is>
-          <t>Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>List of values tests: a non-renewal reason effective next month offered from that date only, an ended reason still shown on the accounts that used it.</t>
         </is>
       </c>
     </row>
@@ -10778,7 +10778,7 @@
       </c>
       <c r="F171" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="G171" s="12" t="inlineStr">
@@ -10788,7 +10788,7 @@
       </c>
       <c r="H171" s="12" t="inlineStr">
         <is>
-          <t>Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Template tests: a Renewal Advice generated after a new template version is activated shows the new layout and its version.</t>
         </is>
       </c>
     </row>
@@ -10990,7 +10990,7 @@
       </c>
       <c r="E7" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F7" s="12" t="inlineStr">
@@ -11000,7 +11000,7 @@
       </c>
       <c r="G7" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours scopes records by role and sales unit (Team Lead sees the unit's, AO his own); BDOI adds the Team Head and Unit Head levels of the reporting hierarchy.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11025,7 +11025,7 @@
       </c>
       <c r="E8" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F8" s="12" t="inlineStr">
@@ -11035,7 +11035,7 @@
       </c>
       <c r="G8" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours scopes records by role and sales unit (Team Lead sees the unit's, AO his own); BDOI adds the Team Head and Unit Head levels of the reporting hierarchy.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11060,7 +11060,7 @@
       </c>
       <c r="E9" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F9" s="12" t="inlineStr">
@@ -11070,7 +11070,7 @@
       </c>
       <c r="G9" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours scopes records by role and sales unit (Team Lead sees the unit's, AO his own); BDOI adds the Team Head and Unit Head levels of the reporting hierarchy.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11095,7 +11095,7 @@
       </c>
       <c r="E10" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F10" s="12" t="inlineStr">
@@ -11105,7 +11105,7 @@
       </c>
       <c r="G10" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours scopes records by role and sales unit (Team Lead sees the unit's, AO his own); BDOI adds the Team Head and Unit Head levels of the reporting hierarchy.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11200,7 +11200,7 @@
       </c>
       <c r="E13" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F13" s="12" t="inlineStr">
@@ -11210,7 +11210,7 @@
       </c>
       <c r="G13" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI ends the session after 30 minutes of inactivity and then shows "Your session timed out"; ours warns 30 minutes before the system log-out, as BRD x.001 reads.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11235,7 +11235,7 @@
       </c>
       <c r="E14" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F14" s="12" t="inlineStr">
@@ -11245,7 +11245,7 @@
       </c>
       <c r="G14" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI ends the session after 30 minutes of inactivity and then shows "Your session timed out"; ours warns 30 minutes before the system log-out, as BRD x.001 reads.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11270,7 +11270,7 @@
       </c>
       <c r="E15" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F15" s="12" t="inlineStr">
@@ -11280,7 +11280,7 @@
       </c>
       <c r="G15" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI ends the session after 30 minutes of inactivity and then shows "Your session timed out"; ours warns 30 minutes before the system log-out, as BRD x.001 reads.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11305,7 +11305,7 @@
       </c>
       <c r="E16" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F16" s="12" t="inlineStr">
@@ -11315,7 +11315,7 @@
       </c>
       <c r="G16" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has Renewal Home, Expiry List, LAMD Reports, Insurer Batches and Letters as separate screens; BDOI puts the bucket lists, uploads (insurer disposition, account update, placement report, hold cover response) and LAMD on one landing page.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11340,7 +11340,7 @@
       </c>
       <c r="E17" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F17" s="12" t="inlineStr">
@@ -11350,7 +11350,7 @@
       </c>
       <c r="G17" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has Renewal Home, Expiry List, LAMD Reports, Insurer Batches and Letters as separate screens; BDOI puts the bucket lists, uploads (insurer disposition, account update, placement report, hold cover response) and LAMD on one landing page.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11375,7 +11375,7 @@
       </c>
       <c r="E18" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F18" s="12" t="inlineStr">
@@ -11385,7 +11385,7 @@
       </c>
       <c r="G18" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has Renewal Home, Expiry List, LAMD Reports, Insurer Batches and Letters as separate screens; BDOI puts the bucket lists, uploads (insurer disposition, account update, placement report, hold cover response) and LAMD on one landing page.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11410,7 +11410,7 @@
       </c>
       <c r="E19" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F19" s="12" t="inlineStr">
@@ -11420,7 +11420,7 @@
       </c>
       <c r="G19" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours shows tiles by status, bucket and expiry window that open filtered lists; BDOI adds the period, market segment and Account Officer filters and a fixed drill-down column set.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11445,7 +11445,7 @@
       </c>
       <c r="E20" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F20" s="12" t="inlineStr">
@@ -11455,7 +11455,7 @@
       </c>
       <c r="G20" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours shows tiles by status, bucket and expiry window that open filtered lists; BDOI adds the period, market segment and Account Officer filters and a fixed drill-down column set.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11480,7 +11480,7 @@
       </c>
       <c r="E21" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F21" s="12" t="inlineStr">
@@ -11490,7 +11490,7 @@
       </c>
       <c r="G21" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours shows tiles by status, bucket and expiry window that open filtered lists; BDOI adds the period, market segment and Account Officer filters and a fixed drill-down column set.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11515,7 +11515,7 @@
       </c>
       <c r="E22" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F22" s="12" t="inlineStr">
@@ -11525,7 +11525,7 @@
       </c>
       <c r="G22" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Premium and commission against budget, variance, growth and adjustments; the system has production against target per team in the New Business dashboard, not a renewal budget.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11550,7 +11550,7 @@
       </c>
       <c r="E23" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F23" s="12" t="inlineStr">
@@ -11560,7 +11560,7 @@
       </c>
       <c r="G23" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Premium and commission against budget, variance, growth and adjustments; the system has production against target per team in the New Business dashboard, not a renewal budget.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11585,7 +11585,7 @@
       </c>
       <c r="E24" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F24" s="12" t="inlineStr">
@@ -11595,7 +11595,7 @@
       </c>
       <c r="G24" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Pipeline by business type (New, Organic, Submitted, Renewal, Deferred) and stages For Survey to For Delivery; the the system stages have other names.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11620,7 +11620,7 @@
       </c>
       <c r="E25" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F25" s="12" t="inlineStr">
@@ -11630,7 +11630,7 @@
       </c>
       <c r="G25" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Pipeline by business type (New, Organic, Submitted, Renewal, Deferred) and stages For Survey to For Delivery; the the system stages have other names.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11655,7 +11655,7 @@
       </c>
       <c r="E26" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F26" s="12" t="inlineStr">
@@ -11665,7 +11665,7 @@
       </c>
       <c r="G26" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours counts accounts expiring in 30, 60, 90 and 140 days; BDOI ages unrenewed accounts by month (prior, current, +1, +2) with premium and commission.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11690,7 +11690,7 @@
       </c>
       <c r="E27" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F27" s="12" t="inlineStr">
@@ -11700,7 +11700,7 @@
       </c>
       <c r="G27" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours counts accounts expiring in 30, 60, 90 and 140 days; BDOI ages unrenewed accounts by month (prior, current, +1, +2) with premium and commission.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11725,7 +11725,7 @@
       </c>
       <c r="E28" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F28" s="12" t="inlineStr">
@@ -11735,7 +11735,7 @@
       </c>
       <c r="G28" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Closing ratio by business type (booked over total accounts) with the in-process, posted and booked pipeline tiers.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11760,7 +11760,7 @@
       </c>
       <c r="E29" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F29" s="12" t="inlineStr">
@@ -11770,7 +11770,7 @@
       </c>
       <c r="G29" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Closing ratio by business type (booked over total accounts) with the in-process, posted and booked pipeline tiers.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11795,7 +11795,7 @@
       </c>
       <c r="E30" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F30" s="12" t="inlineStr">
@@ -11805,7 +11805,7 @@
       </c>
       <c r="G30" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Top 50, 75 or 100 open deals by premium.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11830,7 +11830,7 @@
       </c>
       <c r="E31" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F31" s="12" t="inlineStr">
@@ -11840,7 +11840,7 @@
       </c>
       <c r="G31" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Top 50, 75 or 100 open deals by premium.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11865,7 +11865,7 @@
       </c>
       <c r="E32" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F32" s="12" t="inlineStr">
@@ -11875,7 +11875,7 @@
       </c>
       <c r="G32" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Renewal persistency by count, premium and commission for six months and year to date; the system has a persistency report for submitted policies only.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11900,7 +11900,7 @@
       </c>
       <c r="E33" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F33" s="12" t="inlineStr">
@@ -11910,7 +11910,7 @@
       </c>
       <c r="G33" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Renewal persistency by count, premium and commission for six months and year to date; the system has a persistency report for submitted policies only.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11935,7 +11935,7 @@
       </c>
       <c r="E34" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F34" s="12" t="inlineStr">
@@ -11945,7 +11945,7 @@
       </c>
       <c r="G34" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Production by product line on the dashboard; the system reports production per unit and officer in New Business, not by product line.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -11970,7 +11970,7 @@
       </c>
       <c r="E35" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F35" s="12" t="inlineStr">
@@ -11980,7 +11980,7 @@
       </c>
       <c r="G35" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours shows overdue insurer batches and the insurer extract; BDOI adds the approval monitoring table (Renew As Is, approved, pending, returned, % approval) and pending accounts per insurer.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12005,7 +12005,7 @@
       </c>
       <c r="E36" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F36" s="12" t="inlineStr">
@@ -12015,7 +12015,7 @@
       </c>
       <c r="G36" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours shows overdue insurer batches and the insurer extract; BDOI adds the approval monitoring table (Renew As Is, approved, pending, returned, % approval) and pending accounts per insurer.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12040,7 +12040,7 @@
       </c>
       <c r="E37" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F37" s="12" t="inlineStr">
@@ -12050,7 +12050,7 @@
       </c>
       <c r="G37" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has 34 summary counters of the status report and the home tiles; BDOI adds cards from Cashiering (bounced checks, unapplied payments, refunds) and hold covers expiring in 7 days.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12075,7 +12075,7 @@
       </c>
       <c r="E38" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F38" s="12" t="inlineStr">
@@ -12085,7 +12085,7 @@
       </c>
       <c r="G38" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has 34 summary counters of the status report and the home tiles; BDOI adds cards from Cashiering (bounced checks, unapplied payments, refunds) and hold covers expiring in 7 days.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12110,7 +12110,7 @@
       </c>
       <c r="E39" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F39" s="12" t="inlineStr">
@@ -12120,7 +12120,7 @@
       </c>
       <c r="G39" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI shows four panels Clean, Review, Non-Renewable and All; ours shows tabs by disposition and an Exceptions tab, with the Clean / Review / Exception pill (BRRN.023).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12145,7 +12145,7 @@
       </c>
       <c r="E40" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F40" s="12" t="inlineStr">
@@ -12155,7 +12155,7 @@
       </c>
       <c r="G40" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI shows four panels Clean, Review, Non-Renewable and All; ours shows tabs by disposition and an Exceptions tab, with the Clean / Review / Exception pill (BRRN.023).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12180,7 +12180,7 @@
       </c>
       <c r="E41" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F41" s="12" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="G41" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI shows four panels Clean, Review, Non-Renewable and All; ours shows tabs by disposition and an Exceptions tab, with the Clean / Review / Exception pill (BRRN.023).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12390,7 +12390,7 @@
       </c>
       <c r="E47" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F47" s="12" t="inlineStr">
@@ -12400,7 +12400,7 @@
       </c>
       <c r="G47" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI wants one processing dashboard for New Business and Renewal with a combined view; ours has the Processing Team Lead view per officer on Renewal Home.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12425,7 +12425,7 @@
       </c>
       <c r="E48" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F48" s="12" t="inlineStr">
@@ -12435,7 +12435,7 @@
       </c>
       <c r="G48" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI wants one processing dashboard for New Business and Renewal with a combined view; ours has the Processing Team Lead view per officer on Renewal Home.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12460,7 +12460,7 @@
       </c>
       <c r="E49" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F49" s="12" t="inlineStr">
@@ -12470,7 +12470,7 @@
       </c>
       <c r="G49" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: KPI cards For Placement, For Booking, With and Without Policy, For Releasing, Released, Unreleased, Directly Booked, Returned; the system shows these queues on the New Business placement, booking and e-policy screens, not as cards.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12495,7 +12495,7 @@
       </c>
       <c r="E50" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F50" s="12" t="inlineStr">
@@ -12505,7 +12505,7 @@
       </c>
       <c r="G50" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: KPI cards For Placement, For Booking, With and Without Policy, For Releasing, Released, Unreleased, Directly Booked, Returned; the system shows these queues on the New Business placement, booking and e-policy screens, not as cards.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12530,7 +12530,7 @@
       </c>
       <c r="E51" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F51" s="12" t="inlineStr">
@@ -12540,7 +12540,7 @@
       </c>
       <c r="G51" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Assigned and Unassigned tabs with ageing in business days from Submitted for Placement.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12565,7 +12565,7 @@
       </c>
       <c r="E52" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F52" s="12" t="inlineStr">
@@ -12575,7 +12575,7 @@
       </c>
       <c r="G52" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Assigned and Unassigned tabs with ageing in business days from Submitted for Placement.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12600,7 +12600,7 @@
       </c>
       <c r="E53" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F53" s="12" t="inlineStr">
@@ -12610,7 +12610,7 @@
       </c>
       <c r="G53" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: For Booking drill-down with ageing from the placement date.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12635,7 +12635,7 @@
       </c>
       <c r="E54" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F54" s="12" t="inlineStr">
@@ -12645,7 +12645,7 @@
       </c>
       <c r="G54" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: With / Without Policy drill-down with policy status, TAT status, placement issue and resolution date.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12670,7 +12670,7 @@
       </c>
       <c r="E55" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F55" s="12" t="inlineStr">
@@ -12680,7 +12680,7 @@
       </c>
       <c r="G55" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: With / Without Policy drill-down with policy status, TAT status, placement issue and resolution date.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12705,7 +12705,7 @@
       </c>
       <c r="E56" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F56" s="12" t="inlineStr">
@@ -12715,7 +12715,7 @@
       </c>
       <c r="G56" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Policy transmittal drill-down (sent, pending, unsuccessful) with reason for reject.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12740,7 +12740,7 @@
       </c>
       <c r="E57" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F57" s="12" t="inlineStr">
@@ -12750,7 +12750,7 @@
       </c>
       <c r="G57" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Direct Booking drill-down; the system books directly in New Business.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -12775,7 +12775,7 @@
       </c>
       <c r="E58" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F58" s="12" t="inlineStr">
@@ -12785,7 +12785,7 @@
       </c>
       <c r="G58" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours flags returned accounts and filters them; BDOI adds a Returned card with the reason for return.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13160,7 +13160,7 @@
       </c>
       <c r="E69" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F69" s="12" t="inlineStr">
@@ -13170,7 +13170,7 @@
       </c>
       <c r="G69" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI creates a renewal account per listed account at generation (disposition For Disposition, status In Process Renewal); ours creates a renewal record with a renewal reference, starts nothing until an explicit initiation (BRRN.021) and creates the renewal account when processing starts. BDOI also lists Free-First-Year accounts in process.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13195,7 +13195,7 @@
       </c>
       <c r="E70" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F70" s="12" t="inlineStr">
@@ -13205,7 +13205,7 @@
       </c>
       <c r="G70" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI creates a renewal account per listed account at generation (disposition For Disposition, status In Process Renewal); ours creates a renewal record with a renewal reference, starts nothing until an explicit initiation (BRRN.021) and creates the renewal account when processing starts. BDOI also lists Free-First-Year accounts in process.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13230,7 +13230,7 @@
       </c>
       <c r="E71" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F71" s="12" t="inlineStr">
@@ -13240,7 +13240,7 @@
       </c>
       <c r="G71" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI creates a renewal account per listed account at generation (disposition For Disposition, status In Process Renewal); ours creates a renewal record with a renewal reference, starts nothing until an explicit initiation (BRRN.021) and creates the renewal account when processing starts. BDOI also lists Free-First-Year accounts in process.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13265,7 +13265,7 @@
       </c>
       <c r="E72" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F72" s="12" t="inlineStr">
@@ -13275,7 +13275,7 @@
       </c>
       <c r="G72" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI creates a renewal account per listed account at generation (disposition For Disposition, status In Process Renewal); ours creates a renewal record with a renewal reference, starts nothing until an explicit initiation (BRRN.021) and creates the renewal account when processing starts. BDOI also lists Free-First-Year accounts in process.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13300,7 +13300,7 @@
       </c>
       <c r="E73" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F73" s="12" t="inlineStr">
@@ -13310,7 +13310,7 @@
       </c>
       <c r="G73" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI offers a Refresh Endorsements action that re-reads the mother policy and recalculates; ours creates the renewal account from the policy as of the last posted endorsement and blocks post and RA while an endorsement is in progress.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13335,7 +13335,7 @@
       </c>
       <c r="E74" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F74" s="12" t="inlineStr">
@@ -13345,7 +13345,7 @@
       </c>
       <c r="G74" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI offers a Refresh Endorsements action that re-reads the mother policy and recalculates; ours creates the renewal account from the policy as of the last posted endorsement and blocks post and RA while an endorsement is in progress.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13370,7 +13370,7 @@
       </c>
       <c r="E75" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F75" s="12" t="inlineStr">
@@ -13380,7 +13380,7 @@
       </c>
       <c r="G75" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Same export and print; BDOI fixes the file name RMEL_&lt;MMM&gt;_&lt;YYYY&gt;_&lt;MMDDYYYY&gt;.xlsx, ours does not name the file.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13405,7 +13405,7 @@
       </c>
       <c r="E76" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F76" s="12" t="inlineStr">
@@ -13415,7 +13415,7 @@
       </c>
       <c r="G76" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Same export and print; BDOI fixes the file name RMEL_&lt;MMM&gt;_&lt;YYYY&gt;_&lt;MMDDYYYY&gt;.xlsx, ours does not name the file.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13440,7 +13440,7 @@
       </c>
       <c r="E77" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F77" s="12" t="inlineStr">
@@ -13450,7 +13450,7 @@
       </c>
       <c r="G77" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours creates the renewal account from a renewal record (Create Renewal Account on the record); BDOI lets a user create a renewal account for any expiring account, inception one day after the old expiry and expiry one year later, then sanitises it. Ours keeps the term of the expiring policy.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13475,7 +13475,7 @@
       </c>
       <c r="E78" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F78" s="12" t="inlineStr">
@@ -13485,7 +13485,7 @@
       </c>
       <c r="G78" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours creates the renewal account from a renewal record (Create Renewal Account on the record); BDOI lets a user create a renewal account for any expiring account, inception one day after the old expiry and expiry one year later, then sanitises it. Ours keeps the term of the expiring policy.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13510,7 +13510,7 @@
       </c>
       <c r="E79" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F79" s="12" t="inlineStr">
@@ -13520,7 +13520,7 @@
       </c>
       <c r="G79" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours creates the renewal account from a renewal record (Create Renewal Account on the record); BDOI lets a user create a renewal account for any expiring account, inception one day after the old expiry and expiry one year later, then sanitises it. Ours keeps the term of the expiring policy.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13545,7 +13545,7 @@
       </c>
       <c r="E80" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F80" s="12" t="inlineStr">
@@ -13555,7 +13555,7 @@
       </c>
       <c r="G80" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours checks that no other open renewal exists for the same expiring policy; BDOI checks client number, risk code, PN and expiring policy number (configurable per line, Annex B), tells exact from potential duplicates, warns on manual creation and puts generated ones in Review with a link; a cancelled match does not block.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13580,7 +13580,7 @@
       </c>
       <c r="E81" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F81" s="12" t="inlineStr">
@@ -13590,7 +13590,7 @@
       </c>
       <c r="G81" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours checks that no other open renewal exists for the same expiring policy; BDOI checks client number, risk code, PN and expiring policy number (configurable per line, Annex B), tells exact from potential duplicates, warns on manual creation and puts generated ones in Review with a link; a cancelled match does not block.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13615,7 +13615,7 @@
       </c>
       <c r="E82" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F82" s="12" t="inlineStr">
@@ -13625,7 +13625,7 @@
       </c>
       <c r="G82" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours checks that no other open renewal exists for the same expiring policy; BDOI checks client number, risk code, PN and expiring policy number (configurable per line, Annex B), tells exact from potential duplicates, warns on manual creation and puts generated ones in Review with a link; a cancelled match does not block.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13755,7 +13755,7 @@
       </c>
       <c r="E86" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F86" s="12" t="inlineStr">
@@ -13765,7 +13765,7 @@
       </c>
       <c r="G86" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Several rules differ: missing data is Review in BDOI and Exception in ours; TSI above PHP 250M is Clean / For Quotation in BDOI and Review / For Proposal in ours; any endorsement is Review in BDOI, only an endorsement in progress blocks in ours; PA and GPA are Clean / For Proposal in BDOI only; a total loss is Not for Renewal in BDOI, a manual reason in ours until Claims gives the indicator.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13790,7 +13790,7 @@
       </c>
       <c r="E87" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F87" s="12" t="inlineStr">
@@ -13800,7 +13800,7 @@
       </c>
       <c r="G87" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Several rules differ: missing data is Review in BDOI and Exception in ours; TSI above PHP 250M is Clean / For Quotation in BDOI and Review / For Proposal in ours; any endorsement is Review in BDOI, only an endorsement in progress blocks in ours; PA and GPA are Clean / For Proposal in BDOI only; a total loss is Not for Renewal in BDOI, a manual reason in ours until Claims gives the indicator.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13825,7 +13825,7 @@
       </c>
       <c r="E88" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F88" s="12" t="inlineStr">
@@ -13835,7 +13835,7 @@
       </c>
       <c r="G88" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Several rules differ: missing data is Review in BDOI and Exception in ours; TSI above PHP 250M is Clean / For Quotation in BDOI and Review / For Proposal in ours; any endorsement is Review in BDOI, only an endorsement in progress blocks in ours; PA and GPA are Clean / For Proposal in BDOI only; a total loss is Not for Renewal in BDOI, a manual reason in ours until Claims gives the indicator.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13860,7 +13860,7 @@
       </c>
       <c r="E89" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F89" s="12" t="inlineStr">
@@ -13870,7 +13870,7 @@
       </c>
       <c r="G89" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Several rules differ: missing data is Review in BDOI and Exception in ours; TSI above PHP 250M is Clean / For Quotation in BDOI and Review / For Proposal in ours; any endorsement is Review in BDOI, only an endorsement in progress blocks in ours; PA and GPA are Clean / For Proposal in BDOI only; a total loss is Not for Renewal in BDOI, a manual reason in ours until Claims gives the indicator.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13895,7 +13895,7 @@
       </c>
       <c r="E90" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F90" s="12" t="inlineStr">
@@ -13905,7 +13905,7 @@
       </c>
       <c r="G90" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Third bucket Non-Renewable (BDOI) against Exception (ours, BRRN.023); BDOI sets Clean accounts For Renewal with status For RA Generation (CBG) or Posted (Non-CBG); ours lets the decision matrix propose or apply the disposition and a failed check can never be Clean.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13930,7 +13930,7 @@
       </c>
       <c r="E91" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F91" s="12" t="inlineStr">
@@ -13940,7 +13940,7 @@
       </c>
       <c r="G91" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Third bucket Non-Renewable (BDOI) against Exception (ours, BRRN.023); BDOI sets Clean accounts For Renewal with status For RA Generation (CBG) or Posted (Non-CBG); ours lets the decision matrix propose or apply the disposition and a failed check can never be Clean.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -13965,7 +13965,7 @@
       </c>
       <c r="E92" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F92" s="12" t="inlineStr">
@@ -13975,7 +13975,7 @@
       </c>
       <c r="G92" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Third bucket Non-Renewable (BDOI) against Exception (ours, BRRN.023); BDOI sets Clean accounts For Renewal with status For RA Generation (CBG) or Posted (Non-CBG); ours lets the decision matrix propose or apply the disposition and a failed check can never be Clean.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14000,7 +14000,7 @@
       </c>
       <c r="E93" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F93" s="12" t="inlineStr">
@@ -14010,7 +14010,7 @@
       </c>
       <c r="G93" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Third bucket Non-Renewable (BDOI) against Exception (ours, BRRN.023); BDOI sets Clean accounts For Renewal with status For RA Generation (CBG) or Posted (Non-CBG); ours lets the decision matrix propose or apply the disposition and a failed check can never be Clean.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14035,7 +14035,7 @@
       </c>
       <c r="E94" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F94" s="12" t="inlineStr">
@@ -14045,7 +14045,7 @@
       </c>
       <c r="G94" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Automatic CBG Motor renewal values (Annexes D and E: depreciation, BI/PD tiers, Auto Promo to Regular, DST, VAT, LGT); ours rates the renewal account on the package of the expiring account. BDOI's list for CBG Home and Non-CBG is empty.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14070,7 +14070,7 @@
       </c>
       <c r="E95" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F95" s="12" t="inlineStr">
@@ -14080,7 +14080,7 @@
       </c>
       <c r="G95" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Automatic CBG Motor renewal values (Annexes D and E: depreciation, BI/PD tiers, Auto Promo to Regular, DST, VAT, LGT); ours rates the renewal account on the package of the expiring account. BDOI's list for CBG Home and Non-CBG is empty.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14105,7 +14105,7 @@
       </c>
       <c r="E96" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F96" s="12" t="inlineStr">
@@ -14115,7 +14115,7 @@
       </c>
       <c r="G96" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Automatic CBG Motor renewal values (Annexes D and E: depreciation, BI/PD tiers, Auto Promo to Regular, DST, VAT, LGT); ours rates the renewal account on the package of the expiring account. BDOI's list for CBG Home and Non-CBG is empty.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14140,7 +14140,7 @@
       </c>
       <c r="E97" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F97" s="12" t="inlineStr">
@@ -14150,7 +14150,7 @@
       </c>
       <c r="G97" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: BDOI assigns automatically by team and sub-team with round robin (Annex F) for Marketing and Processing; ours lets the Team Lead assign (BRD 1.005, 3.005) and does not assign CBG accounts.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14175,7 +14175,7 @@
       </c>
       <c r="E98" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F98" s="12" t="inlineStr">
@@ -14185,7 +14185,7 @@
       </c>
       <c r="G98" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: BDOI assigns automatically by team and sub-team with round robin (Annex F) for Marketing and Processing; ours lets the Team Lead assign (BRD 1.005, 3.005) and does not assign CBG accounts.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14210,7 +14210,7 @@
       </c>
       <c r="E99" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F99" s="12" t="inlineStr">
@@ -14220,7 +14220,7 @@
       </c>
       <c r="G99" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: BDOI assigns automatically by team and sub-team with round robin (Annex F) for Marketing and Processing; ours lets the Team Lead assign (BRD 1.005, 3.005) and does not assign CBG accounts.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14315,7 +14315,7 @@
       </c>
       <c r="E102" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F102" s="12" t="inlineStr">
@@ -14325,7 +14325,7 @@
       </c>
       <c r="G102" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI's transfer is a referral: the renewal stays with its unit and the receiving unit opens a New Business account; ours moves the renewal to the receiving unit (BRD 1.006, 1.007, 2.005).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14350,7 +14350,7 @@
       </c>
       <c r="E103" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F103" s="12" t="inlineStr">
@@ -14360,7 +14360,7 @@
       </c>
       <c r="G103" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Same request with target unit and justification; BDOI adds a Transfer Request Number and status Pending Acceptance.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14385,7 +14385,7 @@
       </c>
       <c r="E104" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F104" s="12" t="inlineStr">
@@ -14395,7 +14395,7 @@
       </c>
       <c r="G104" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Same request with target unit and justification; BDOI adds a Transfer Request Number and status Pending Acceptance.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14420,7 +14420,7 @@
       </c>
       <c r="E105" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F105" s="12" t="inlineStr">
@@ -14430,7 +14430,7 @@
       </c>
       <c r="G105" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours accepts or declines with remarks; BDOI adds Return for Clarification.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14455,7 +14455,7 @@
       </c>
       <c r="E106" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F106" s="12" t="inlineStr">
@@ -14465,7 +14465,7 @@
       </c>
       <c r="G106" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours accepts or declines with remarks; BDOI adds Return for Clarification.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14490,7 +14490,7 @@
       </c>
       <c r="E107" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F107" s="12" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="G107" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Creation of a New Business account from the copied renewal data on acceptance.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14525,7 +14525,7 @@
       </c>
       <c r="E108" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F108" s="12" t="inlineStr">
@@ -14535,7 +14535,7 @@
       </c>
       <c r="G108" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has Transfers (incoming and outgoing); BDOI lists the statuses Draft to Returned for Clarification and the New Business account number.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14560,7 +14560,7 @@
       </c>
       <c r="E109" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F109" s="12" t="inlineStr">
@@ -14570,7 +14570,7 @@
       </c>
       <c r="G109" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has Transfers (incoming and outgoing); BDOI lists the statuses Draft to Returned for Clarification and the New Business account number.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14595,7 +14595,7 @@
       </c>
       <c r="E110" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F110" s="12" t="inlineStr">
@@ -14605,7 +14605,7 @@
       </c>
       <c r="G110" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours notifies the request and the decision; BDOI also notifies a return for clarification.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14630,7 +14630,7 @@
       </c>
       <c r="E111" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F111" s="12" t="inlineStr">
@@ -14640,7 +14640,7 @@
       </c>
       <c r="G111" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours uploads LAMD reports of paid-off and RMU loans; BDOI uploads the full CBG loan list (excluding personal loans) and the paid-off list and derives the loan status (Active, Loan Fully Paid, RMU, Unmatched); required fields PN and AO code, plus serial and motor number for Motor.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14665,7 +14665,7 @@
       </c>
       <c r="E112" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F112" s="12" t="inlineStr">
@@ -14675,7 +14675,7 @@
       </c>
       <c r="G112" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours uploads LAMD reports of paid-off and RMU loans; BDOI uploads the full CBG loan list (excluding personal loans) and the paid-off list and derives the loan status (Active, Loan Fully Paid, RMU, Unmatched); required fields PN and AO code, plus serial and motor number for Motor.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14700,7 +14700,7 @@
       </c>
       <c r="E113" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F113" s="12" t="inlineStr">
@@ -14710,7 +14710,7 @@
       </c>
       <c r="G113" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours uploads LAMD reports of paid-off and RMU loans; BDOI uploads the full CBG loan list (excluding personal loans) and the paid-off list and derives the loan status (Active, Loan Fully Paid, RMU, Unmatched); required fields PN and AO code, plus serial and motor number for Motor.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14735,7 +14735,7 @@
       </c>
       <c r="E114" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F114" s="12" t="inlineStr">
@@ -14745,7 +14745,7 @@
       </c>
       <c r="G114" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours matches on PN; BDOI matches CBG Motor on PN, serial number and motor number.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14770,7 +14770,7 @@
       </c>
       <c r="E115" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F115" s="12" t="inlineStr">
@@ -14780,7 +14780,7 @@
       </c>
       <c r="G115" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours matches on PN; BDOI matches CBG Motor on PN, serial number and motor number.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14805,7 +14805,7 @@
       </c>
       <c r="E116" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F116" s="12" t="inlineStr">
@@ -14815,7 +14815,7 @@
       </c>
       <c r="G116" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours shows the match results of each report; BDOI fixes the file-level summary columns, statuses and the result file name.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14840,7 +14840,7 @@
       </c>
       <c r="E117" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F117" s="12" t="inlineStr">
@@ -14850,7 +14850,7 @@
       </c>
       <c r="G117" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Record-level results with matching and processing status and the reason.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14875,7 +14875,7 @@
       </c>
       <c r="E118" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F118" s="12" t="inlineStr">
@@ -14885,7 +14885,7 @@
       </c>
       <c r="G118" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI keeps a cumulative list of paid-off accounts without duplicates; ours keeps the lines of each report.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14910,7 +14910,7 @@
       </c>
       <c r="E119" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F119" s="12" t="inlineStr">
@@ -14920,7 +14920,7 @@
       </c>
       <c r="G119" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: BDOFC and BDOSOLD report upload (PN, assured's name, remarks).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14945,7 +14945,7 @@
       </c>
       <c r="E120" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F120" s="12" t="inlineStr">
@@ -14955,7 +14955,7 @@
       </c>
       <c r="G120" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: BDOFC and BDOSOLD report upload (PN, assured's name, remarks).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -14980,7 +14980,7 @@
       </c>
       <c r="E121" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F121" s="12" t="inlineStr">
@@ -14990,7 +14990,7 @@
       </c>
       <c r="G121" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: BDOFC / SOLD matching on PN; BDOI does not say what a match changes.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15015,7 +15015,7 @@
       </c>
       <c r="E122" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F122" s="12" t="inlineStr">
@@ -15025,7 +15025,7 @@
       </c>
       <c r="G122" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Upload summary of the BDOFC / SOLD files.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15050,7 +15050,7 @@
       </c>
       <c r="E123" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F123" s="12" t="inlineStr">
@@ -15060,7 +15060,7 @@
       </c>
       <c r="G123" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Record-level results of the BDOFC / SOLD files.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15085,7 +15085,7 @@
       </c>
       <c r="E124" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F124" s="12" t="inlineStr">
@@ -15095,7 +15095,7 @@
       </c>
       <c r="G124" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours uploads the insurer's response file keyed by the renewal reference; BDOI fixes the CBG layout of Annex H (17 fields) and a Non-CBG layout, with its messages.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15120,7 +15120,7 @@
       </c>
       <c r="E125" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F125" s="12" t="inlineStr">
@@ -15130,7 +15130,7 @@
       </c>
       <c r="G125" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours uploads the insurer's response file keyed by the renewal reference; BDOI fixes the CBG layout of Annex H (17 fields) and a Non-CBG layout, with its messages.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15155,7 +15155,7 @@
       </c>
       <c r="E126" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F126" s="12" t="inlineStr">
@@ -15165,7 +15165,7 @@
       </c>
       <c r="G126" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI maps nine insurer dispositions to bucket and disposition (Rejected goes to Review / For Disposition, Total Loss to Non-Renewable); ours has three responses (Renew As Is, Revise, Reject; Reject tags Not for Renewal or returns to Marketing).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15190,7 +15190,7 @@
       </c>
       <c r="E127" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F127" s="12" t="inlineStr">
@@ -15200,7 +15200,7 @@
       </c>
       <c r="G127" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI maps nine insurer dispositions to bucket and disposition (Rejected goes to Review / For Disposition, Total Loss to Non-Renewable); ours has three responses (Renew As Is, Revise, Reject; Reject tags Not for Renewal or returns to Marketing).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15225,7 +15225,7 @@
       </c>
       <c r="E128" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F128" s="12" t="inlineStr">
@@ -15235,7 +15235,7 @@
       </c>
       <c r="G128" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI maps nine insurer dispositions to bucket and disposition (Rejected goes to Review / For Disposition, Total Loss to Non-Renewable); ours has three responses (Renew As Is, Revise, Reject; Reject tags Not for Renewal or returns to Marketing).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15260,7 +15260,7 @@
       </c>
       <c r="E129" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F129" s="12" t="inlineStr">
@@ -15270,7 +15270,7 @@
       </c>
       <c r="G129" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Upload summary of the insurer disposition files (numbered 012.03 inside FRRN.013 in BDOI's FRS).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15295,7 +15295,7 @@
       </c>
       <c r="E130" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F130" s="12" t="inlineStr">
@@ -15305,7 +15305,7 @@
       </c>
       <c r="G130" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Record-level view with "Record not found" (numbered 012.04 inside FRRN.013).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15330,7 +15330,7 @@
       </c>
       <c r="E131" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F131" s="12" t="inlineStr">
@@ -15340,7 +15340,7 @@
       </c>
       <c r="G131" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Both show every renewal field and the account history (policies, endorsements, payments, claims) with download and print; BDOI adds the refund link.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15365,7 +15365,7 @@
       </c>
       <c r="E132" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F132" s="12" t="inlineStr">
@@ -15375,7 +15375,7 @@
       </c>
       <c r="G132" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Both show every renewal field and the account history (policies, endorsements, payments, claims) with download and print; BDOI adds the refund link.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15400,7 +15400,7 @@
       </c>
       <c r="E133" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F133" s="12" t="inlineStr">
@@ -15410,7 +15410,7 @@
       </c>
       <c r="G133" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Both show every renewal field and the account history (policies, endorsements, payments, claims) with download and print; BDOI adds the refund link.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15435,7 +15435,7 @@
       </c>
       <c r="E134" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F134" s="12" t="inlineStr">
@@ -15445,7 +15445,7 @@
       </c>
       <c r="G134" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has five dispositions (with Lost Business) and ten non-renewal reasons and locks the account when the RA is generated (BRD 2.004.9); BDOI has four dispositions, 21 reasons and locks when posted and placed. File types and messages are BDOI's.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15470,7 +15470,7 @@
       </c>
       <c r="E135" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F135" s="12" t="inlineStr">
@@ -15480,7 +15480,7 @@
       </c>
       <c r="G135" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has five dispositions (with Lost Business) and ten non-renewal reasons and locks the account when the RA is generated (BRD 2.004.9); BDOI has four dispositions, 21 reasons and locks when posted and placed. File types and messages are BDOI's.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15505,7 +15505,7 @@
       </c>
       <c r="E136" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F136" s="12" t="inlineStr">
@@ -15515,7 +15515,7 @@
       </c>
       <c r="G136" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has five dispositions (with Lost Business) and ten non-renewal reasons and locks the account when the RA is generated (BRD 2.004.9); BDOI has four dispositions, 21 reasons and locks when posted and placed. File types and messages are BDOI's.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15540,7 +15540,7 @@
       </c>
       <c r="E137" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F137" s="12" t="inlineStr">
@@ -15550,7 +15550,7 @@
       </c>
       <c r="G137" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has five dispositions (with Lost Business) and ten non-renewal reasons and locks the account when the RA is generated (BRD 2.004.9); BDOI has four dispositions, 21 reasons and locks when posted and placed. File types and messages are BDOI's.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15575,7 +15575,7 @@
       </c>
       <c r="E138" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F138" s="12" t="inlineStr">
@@ -15585,7 +15585,7 @@
       </c>
       <c r="G138" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Allocation of the renewal to several insurers by percentage (total 100%) or amount (total = TSI); the system takes the insurers and shares from the package.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15610,7 +15610,7 @@
       </c>
       <c r="E139" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F139" s="12" t="inlineStr">
@@ -15620,7 +15620,7 @@
       </c>
       <c r="G139" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Allocation of the renewal to several insurers by percentage (total 100%) or amount (total = TSI); the system takes the insurers and shares from the package.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15645,7 +15645,7 @@
       </c>
       <c r="E140" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F140" s="12" t="inlineStr">
@@ -15655,7 +15655,7 @@
       </c>
       <c r="G140" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: For Booking Only tag with policy number, OR number, policy document and full payment checks and an override approval; the system books directly in New Business.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15680,7 +15680,7 @@
       </c>
       <c r="E141" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F141" s="12" t="inlineStr">
@@ -15690,7 +15690,7 @@
       </c>
       <c r="G141" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: For Booking Only tag with policy number, OR number, policy document and full payment checks and an override approval; the system books directly in New Business.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15715,7 +15715,7 @@
       </c>
       <c r="E142" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F142" s="12" t="inlineStr">
@@ -15725,7 +15725,7 @@
       </c>
       <c r="G142" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Direct-to-Insurer Payment tag with blanket approval or Unit Head approval; the system has the direct payment tag of New Business without the approval route. Ours has only the non-renewal reason Direct to Insurer.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15750,7 +15750,7 @@
       </c>
       <c r="E143" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F143" s="12" t="inlineStr">
@@ -15760,7 +15760,7 @@
       </c>
       <c r="G143" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Direct-to-Insurer Payment tag with blanket approval or Unit Head approval; the system has the direct payment tag of New Business without the approval route. Ours has only the non-renewal reason Direct to Insurer.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15820,7 +15820,7 @@
       </c>
       <c r="E145" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F145" s="12" t="inlineStr">
@@ -15830,7 +15830,7 @@
       </c>
       <c r="G145" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours uploads dispositioned files on the Processing Worklist; BDOI has a general Renewal Update upload with a downloadable template on the landing page.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15855,7 +15855,7 @@
       </c>
       <c r="E146" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F146" s="12" t="inlineStr">
@@ -15865,7 +15865,7 @@
       </c>
       <c r="G146" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours uploads dispositioned files on the Processing Worklist; BDOI has a general Renewal Update upload with a downloadable template on the landing page.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15925,7 +15925,7 @@
       </c>
       <c r="E148" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F148" s="12" t="inlineStr">
@@ -15935,7 +15935,7 @@
       </c>
       <c r="G148" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Upload summary columns and statuses.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15960,7 +15960,7 @@
       </c>
       <c r="E149" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F149" s="12" t="inlineStr">
@@ -15970,7 +15970,7 @@
       </c>
       <c r="G149" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Record-level results with filter, sort and search.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -15995,7 +15995,7 @@
       </c>
       <c r="E150" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F150" s="12" t="inlineStr">
@@ -16005,7 +16005,7 @@
       </c>
       <c r="G150" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours pushes the account to the unit's TLs (Review in Progress); BDOI makes the user pick the approver and names the status Submitted for Posting.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16030,7 +16030,7 @@
       </c>
       <c r="E151" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F151" s="12" t="inlineStr">
@@ -16040,7 +16040,7 @@
       </c>
       <c r="G151" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours pushes the account to the unit's TLs (Review in Progress); BDOI makes the user pick the approver and names the status Submitted for Posting.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16065,7 +16065,7 @@
       </c>
       <c r="E152" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F152" s="12" t="inlineStr">
@@ -16075,7 +16075,7 @@
       </c>
       <c r="G152" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours sends For Quotation and For Proposal to the New Business quotation or proposal request; BDOI generates a Quick or Full Proposal from the renewal with file names and two or three signatories by TSI (500M).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16100,7 +16100,7 @@
       </c>
       <c r="E153" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F153" s="12" t="inlineStr">
@@ -16110,7 +16110,7 @@
       </c>
       <c r="G153" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours sends For Quotation and For Proposal to the New Business quotation or proposal request; BDOI generates a Quick or Full Proposal from the renewal with file names and two or three signatories by TSI (500M).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16135,7 +16135,7 @@
       </c>
       <c r="E154" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F154" s="12" t="inlineStr">
@@ -16145,7 +16145,7 @@
       </c>
       <c r="G154" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours sends For Quotation and For Proposal to the New Business quotation or proposal request; BDOI generates a Quick or Full Proposal from the renewal with file names and two or three signatories by TSI (500M).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16170,7 +16170,7 @@
       </c>
       <c r="E155" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F155" s="12" t="inlineStr">
@@ -16180,7 +16180,7 @@
       </c>
       <c r="G155" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI sends the proposal through CCM with six delivery statuses; the system sends by its own e-mail with a send log.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16205,7 +16205,7 @@
       </c>
       <c r="E156" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F156" s="12" t="inlineStr">
@@ -16215,7 +16215,7 @@
       </c>
       <c r="G156" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI sends the proposal through CCM with six delivery statuses; the system sends by its own e-mail with a send log.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16240,7 +16240,7 @@
       </c>
       <c r="E157" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F157" s="12" t="inlineStr">
@@ -16250,7 +16250,7 @@
       </c>
       <c r="G157" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI sends For Quotation to TSU with Team Lead approval, TSU officer, comparative table and proposal; ours sends For Proposal to the non-package proposal request (TSU) and For Quotation to the package quotation: the two words are swapped (sheet 8).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16275,7 +16275,7 @@
       </c>
       <c r="E158" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F158" s="12" t="inlineStr">
@@ -16285,7 +16285,7 @@
       </c>
       <c r="G158" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI sends For Quotation to TSU with Team Lead approval, TSU officer, comparative table and proposal; ours sends For Proposal to the non-package proposal request (TSU) and For Quotation to the package quotation: the two words are swapped (sheet 8).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16310,7 +16310,7 @@
       </c>
       <c r="E159" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F159" s="12" t="inlineStr">
@@ -16320,7 +16320,7 @@
       </c>
       <c r="G159" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI records the client's answer to the proposal (Pending, Accepted, Rejected, Request for Revision; rejected becomes Not for Renewal, Lost Business); ours closes the renewal as Lost when the quotation is declined.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16345,7 +16345,7 @@
       </c>
       <c r="E160" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F160" s="12" t="inlineStr">
@@ -16355,7 +16355,7 @@
       </c>
       <c r="G160" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI records the client's answer to the proposal (Pending, Accepted, Rejected, Request for Revision; rejected becomes Not for Renewal, Lost Business); ours closes the renewal as Lost when the quotation is declined.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16660,7 +16660,7 @@
       </c>
       <c r="E169" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F169" s="12" t="inlineStr">
@@ -16670,7 +16670,7 @@
       </c>
       <c r="G169" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours lets the user choose First or Second Notice; BDOI determines the notice (Annex M: 75 and 45 days before expiry), names the file &lt;Product&gt;_RA_&lt;Notice#&gt;_&lt;Ref&gt;_&lt;Date&gt;.pdf and uses four approved RA templates by line (Annex L).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16695,7 +16695,7 @@
       </c>
       <c r="E170" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F170" s="12" t="inlineStr">
@@ -16705,7 +16705,7 @@
       </c>
       <c r="G170" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours lets the user choose First or Second Notice; BDOI determines the notice (Annex M: 75 and 45 days before expiry), names the file &lt;Product&gt;_RA_&lt;Notice#&gt;_&lt;Ref&gt;_&lt;Date&gt;.pdf and uses four approved RA templates by line (Annex L).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16730,7 +16730,7 @@
       </c>
       <c r="E171" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F171" s="12" t="inlineStr">
@@ -16740,7 +16740,7 @@
       </c>
       <c r="G171" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours lets the user choose First or Second Notice; BDOI determines the notice (Annex M: 75 and 45 days before expiry), names the file &lt;Product&gt;_RA_&lt;Notice#&gt;_&lt;Ref&gt;_&lt;Date&gt;.pdf and uses four approved RA templates by line (Annex L).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16765,7 +16765,7 @@
       </c>
       <c r="E172" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F172" s="12" t="inlineStr">
@@ -16775,7 +16775,7 @@
       </c>
       <c r="G172" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours lets the user choose First or Second Notice; BDOI determines the notice (Annex M: 75 and 45 days before expiry), names the file &lt;Product&gt;_RA_&lt;Notice#&gt;_&lt;Ref&gt;_&lt;Date&gt;.pdf and uses four approved RA templates by line (Annex L).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16800,7 +16800,7 @@
       </c>
       <c r="E173" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F173" s="12" t="inlineStr">
@@ -16810,7 +16810,7 @@
       </c>
       <c r="G173" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI sends the RA through CCM with delivery statuses; the system sends a protected e-mail and the password in a separate e-mail.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16835,7 +16835,7 @@
       </c>
       <c r="E174" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F174" s="12" t="inlineStr">
@@ -16845,7 +16845,7 @@
       </c>
       <c r="G174" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI sends the RA through CCM with delivery statuses; the system sends a protected e-mail and the password in a separate e-mail.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16870,7 +16870,7 @@
       </c>
       <c r="E175" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F175" s="12" t="inlineStr">
@@ -16880,7 +16880,7 @@
       </c>
       <c r="G175" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has the RA, NAL, Not for Renewal Letter, NRNS reminder and non-acceptance letter; FFY reminder and SFU letters appear only for submitted policies (FR-RN-090). Eligibility and schedules differ (Annex M, sheet 8).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16905,7 +16905,7 @@
       </c>
       <c r="E176" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F176" s="12" t="inlineStr">
@@ -16915,7 +16915,7 @@
       </c>
       <c r="G176" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has the RA, NAL, Not for Renewal Letter, NRNS reminder and non-acceptance letter; FFY reminder and SFU letters appear only for submitted policies (FR-RN-090). Eligibility and schedules differ (Annex M, sheet 8).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16940,7 +16940,7 @@
       </c>
       <c r="E177" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F177" s="12" t="inlineStr">
@@ -16950,7 +16950,7 @@
       </c>
       <c r="G177" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Same generation, storage, preview and resend; BDOI fixes the file name &lt;Product&gt;_&lt;Letter Type&gt;_&lt;Ref&gt;_&lt;Date&gt;.pdf and the messages; channel CCM against the system e-mail.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -16975,7 +16975,7 @@
       </c>
       <c r="E178" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F178" s="12" t="inlineStr">
@@ -16985,7 +16985,7 @@
       </c>
       <c r="G178" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Same generation, storage, preview and resend; BDOI fixes the file name &lt;Product&gt;_&lt;Letter Type&gt;_&lt;Ref&gt;_&lt;Date&gt;.pdf and the messages; channel CCM against the system e-mail.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17010,7 +17010,7 @@
       </c>
       <c r="E179" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F179" s="12" t="inlineStr">
@@ -17020,7 +17020,7 @@
       </c>
       <c r="G179" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI's password: individuals - first three letters of the first and last names in capitals; corporate - eight random characters (one lower case, one upper case, one special, five digits). the system generates a random 12-character password, pending the convention (Q07).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17045,7 +17045,7 @@
       </c>
       <c r="E180" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F180" s="12" t="inlineStr">
@@ -17055,7 +17055,7 @@
       </c>
       <c r="G180" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI's password: individuals - first three letters of the first and last names in capitals; corporate - eight random characters (one lower case, one upper case, one special, five digits). the system generates a random 12-character password, pending the convention (Q07).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17080,7 +17080,7 @@
       </c>
       <c r="E181" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F181" s="12" t="inlineStr">
@@ -17090,7 +17090,7 @@
       </c>
       <c r="G181" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI's password: individuals - first three letters of the first and last names in capitals; corporate - eight random characters (one lower case, one upper case, one special, five digits). the system generates a random 12-character password, pending the convention (Q07).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17115,7 +17115,7 @@
       </c>
       <c r="E182" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F182" s="12" t="inlineStr">
@@ -17125,7 +17125,7 @@
       </c>
       <c r="G182" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours records the acceptance with its method and evidence; BDOI uses statuses (Pending, Accepted, Rejected, Request for Revision, Not Applicable), exempts CBG Home and FFY accounts (they go to For Billing Generation) and sends the Non-Renewal Letter on rejection.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17150,7 +17150,7 @@
       </c>
       <c r="E183" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F183" s="12" t="inlineStr">
@@ -17160,7 +17160,7 @@
       </c>
       <c r="G183" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours records the acceptance with its method and evidence; BDOI uses statuses (Pending, Accepted, Rejected, Request for Revision, Not Applicable), exempts CBG Home and FFY accounts (they go to For Billing Generation) and sends the Non-Renewal Letter on rejection.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17185,7 +17185,7 @@
       </c>
       <c r="E184" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F184" s="12" t="inlineStr">
@@ -17195,7 +17195,7 @@
       </c>
       <c r="G184" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI adds a second approval after acceptance (Submitted for Approval), auto-submits CBG Motor on payment and requires the payment confirmation for Non-CBG; ours moves the accepted account to placement and booking once the payment rules are met, without a second approval.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17220,7 +17220,7 @@
       </c>
       <c r="E185" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F185" s="12" t="inlineStr">
@@ -17230,7 +17230,7 @@
       </c>
       <c r="G185" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI adds a second approval after acceptance (Submitted for Approval), auto-submits CBG Motor on payment and requires the payment confirmation for Non-CBG; ours moves the accepted account to placement and booking once the payment rules are met, without a second approval.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17255,7 +17255,7 @@
       </c>
       <c r="E186" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F186" s="12" t="inlineStr">
@@ -17265,7 +17265,7 @@
       </c>
       <c r="G186" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Scheduled CLPC billing (CBG Home daily at 10 days before expiry; FFY Motor on the 10th and 25th), Built-in and Non-Built-in files; the system creates the CLPC billing batch on demand and the file is sent outside the system.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17290,7 +17290,7 @@
       </c>
       <c r="E187" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F187" s="12" t="inlineStr">
@@ -17300,7 +17300,7 @@
       </c>
       <c r="G187" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Scheduled CLPC billing (CBG Home daily at 10 days before expiry; FFY Motor on the 10th and 25th), Built-in and Non-Built-in files; the system creates the CLPC billing batch on demand and the file is sent outside the system.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17325,7 +17325,7 @@
       </c>
       <c r="E188" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F188" s="12" t="inlineStr">
@@ -17335,7 +17335,7 @@
       </c>
       <c r="G188" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Manual billing file with a From / To window of at most 31 days.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17360,7 +17360,7 @@
       </c>
       <c r="E189" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F189" s="12" t="inlineStr">
@@ -17370,7 +17370,7 @@
       </c>
       <c r="G189" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Sending the billing file with delivery status (Annex S e-mail).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17395,7 +17395,7 @@
       </c>
       <c r="E190" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F190" s="12" t="inlineStr">
@@ -17405,7 +17405,7 @@
       </c>
       <c r="G190" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours reads the payment status of the payment gate; BDOI names Paid, Partially Paid and Unpaid from the outstanding balance.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17430,7 +17430,7 @@
       </c>
       <c r="E191" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F191" s="12" t="inlineStr">
@@ -17440,7 +17440,7 @@
       </c>
       <c r="G191" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI moves a paid CBG renewal to Submitted for Placement automatically; ours moves an accepted renewal to placement and booking once the payment rules are met and leaves the placement itself to the user.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17500,7 +17500,7 @@
       </c>
       <c r="E193" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F193" s="12" t="inlineStr">
@@ -17510,7 +17510,7 @@
       </c>
       <c r="G193" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: One slip per insurer per account and a consolidated Excel file per insurer for packaged accounts, excluding For Booking Only; the system makes one slip per insurer branch.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17535,7 +17535,7 @@
       </c>
       <c r="E194" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F194" s="12" t="inlineStr">
@@ -17545,7 +17545,7 @@
       </c>
       <c r="G194" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: One slip per insurer per account and a consolidated Excel file per insurer for packaged accounts, excluding For Booking Only; the system makes one slip per insurer branch.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17570,7 +17570,7 @@
       </c>
       <c r="E195" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F195" s="12" t="inlineStr">
@@ -17580,7 +17580,7 @@
       </c>
       <c r="G195" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Placement slip file name and stored details; BDOI's example name carries two product codes.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17605,7 +17605,7 @@
       </c>
       <c r="E196" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F196" s="12" t="inlineStr">
@@ -17615,7 +17615,7 @@
       </c>
       <c r="G196" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Consolidated placement file per insurer; BDOI's example is a.pdf with a reference number although the file is an.xlsx per insurer.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17640,7 +17640,7 @@
       </c>
       <c r="E197" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F197" s="12" t="inlineStr">
@@ -17650,7 +17650,7 @@
       </c>
       <c r="G197" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Automatic upload of placement files through MFT; ours has no file-transfer channel with insurers (on hold).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17675,7 +17675,7 @@
       </c>
       <c r="E198" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F198" s="12" t="inlineStr">
@@ -17685,7 +17685,7 @@
       </c>
       <c r="G198" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Sending placement files through CCM with recipients from Insurer Maintenance; the system sends the slips by e-mail.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17710,7 +17710,7 @@
       </c>
       <c r="E199" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F199" s="12" t="inlineStr">
@@ -17720,7 +17720,7 @@
       </c>
       <c r="G199" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Sending placement files through CCM with recipients from Insurer Maintenance; the system sends the slips by e-mail.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17745,7 +17745,7 @@
       </c>
       <c r="E200" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F200" s="12" t="inlineStr">
@@ -17755,7 +17755,7 @@
       </c>
       <c r="G200" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours sets a reply due date for insurer batches and alerts when overdue; BDOI measures placement TAT in business days (3 packaged, 10 non-package, 3PM cut-off) with a With Issue tag and resolution date.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17780,7 +17780,7 @@
       </c>
       <c r="E201" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F201" s="12" t="inlineStr">
@@ -17790,7 +17790,7 @@
       </c>
       <c r="G201" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours sets a reply due date for insurer batches and alerts when overdue; BDOI measures placement TAT in business days (3 packaged, 10 non-package, 3PM cut-off) with a With Issue tag and resolution date.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17815,7 +17815,7 @@
       </c>
       <c r="E202" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F202" s="12" t="inlineStr">
@@ -17825,7 +17825,7 @@
       </c>
       <c r="G202" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Placement response by upload or MFT, matched on the renewal reference; ours covers the insurer's renewal response before the RA, not the placement response.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17850,7 +17850,7 @@
       </c>
       <c r="E203" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F203" s="12" t="inlineStr">
@@ -17860,7 +17860,7 @@
       </c>
       <c r="G203" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI books the account and locks it when the insurer approves the placement; ours keeps booking a user action (Walkthrough addendum p.4).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17885,7 +17885,7 @@
       </c>
       <c r="E204" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F204" s="12" t="inlineStr">
@@ -17895,7 +17895,7 @@
       </c>
       <c r="G204" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Rejected placement with seven reasons, status Rejected Placement, return to Marketing or cancel the placement.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17920,7 +17920,7 @@
       </c>
       <c r="E205" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F205" s="12" t="inlineStr">
@@ -17930,7 +17930,7 @@
       </c>
       <c r="G205" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Summary of the placement response files.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17955,7 +17955,7 @@
       </c>
       <c r="E206" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F206" s="12" t="inlineStr">
@@ -17965,7 +17965,7 @@
       </c>
       <c r="G206" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Record-level view of the placement responses.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -17990,7 +17990,7 @@
       </c>
       <c r="E207" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F207" s="12" t="inlineStr">
@@ -18000,7 +18000,7 @@
       </c>
       <c r="G207" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours returns from processing to the AO or Team Lead with five return reasons; BDOI returns from Submitted for Placement and Rejected Placement with status Returned - Renewal and 39 reasons (Annex V).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18025,7 +18025,7 @@
       </c>
       <c r="E208" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F208" s="12" t="inlineStr">
@@ -18035,7 +18035,7 @@
       </c>
       <c r="G208" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours returns from processing to the AO or Team Lead with five return reasons; BDOI returns from Submitted for Placement and Rejected Placement with status Returned - Renewal and 39 reasons (Annex V).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18060,7 +18060,7 @@
       </c>
       <c r="E209" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F209" s="12" t="inlineStr">
@@ -18070,7 +18070,7 @@
       </c>
       <c r="G209" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Insurance Advice for mortgaged accounts when the placement is sent, versioned on change; the system generates it for mortgaged accounts on the event set by a parameter (policy issue by default).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18095,7 +18095,7 @@
       </c>
       <c r="E210" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F210" s="12" t="inlineStr">
@@ -18105,7 +18105,7 @@
       </c>
       <c r="G210" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Insurance Advice for mortgaged accounts when the placement is sent, versioned on change; the system generates it for mortgaged accounts on the event set by a parameter (policy issue by default).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18130,7 +18130,7 @@
       </c>
       <c r="E211" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F211" s="12" t="inlineStr">
@@ -18140,7 +18140,7 @@
       </c>
       <c r="G211" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Sending the Insurance Advice through CCM with CC recipients; the system sends by e-mail.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18165,7 +18165,7 @@
       </c>
       <c r="E212" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F212" s="12" t="inlineStr">
@@ -18175,7 +18175,7 @@
       </c>
       <c r="G212" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: E-policy processing in the Renewal FRS; ours refers to New Business issuance.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18200,7 +18200,7 @@
       </c>
       <c r="E213" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F213" s="12" t="inlineStr">
@@ -18210,7 +18210,7 @@
       </c>
       <c r="G213" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: One summary text file and one ZIP per upload, or MFT; the system uploads policy PDFs matched on the account reference in the file name.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18235,7 +18235,7 @@
       </c>
       <c r="E214" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F214" s="12" t="inlineStr">
@@ -18245,7 +18245,7 @@
       </c>
       <c r="G214" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Receipt summary of e-policy files.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18270,7 +18270,7 @@
       </c>
       <c r="E215" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F215" s="12" t="inlineStr">
@@ -18280,7 +18280,7 @@
       </c>
       <c r="G215" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Record-level view of e-policy files.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18305,7 +18305,7 @@
       </c>
       <c r="E216" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F216" s="12" t="inlineStr">
@@ -18315,7 +18315,7 @@
       </c>
       <c r="G216" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Bulk e-policy sending through CCM with eligibility checks; the system sends encrypted e-policies by e-mail.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18340,7 +18340,7 @@
       </c>
       <c r="E217" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F217" s="12" t="inlineStr">
@@ -18350,7 +18350,7 @@
       </c>
       <c r="G217" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Batch upload of e-policy numbers with a duplicate check across active accounts and an exception report.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18515,7 +18515,7 @@
       </c>
       <c r="E222" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F222" s="12" t="inlineStr">
@@ -18525,7 +18525,7 @@
       </c>
       <c r="G222" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI defaults 30 days (Non-CBG) and 90 days (CBG), and 30 (CBG Home) or 60 (CBG Motor) for transferred accounts; ours offers 30 or 60 days, 30 by default.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18550,7 +18550,7 @@
       </c>
       <c r="E223" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F223" s="12" t="inlineStr">
@@ -18560,7 +18560,7 @@
       </c>
       <c r="G223" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI defaults 30 days (Non-CBG) and 90 days (CBG), and 30 (CBG Home) or 60 (CBG Motor) for transferred accounts; ours offers 30 or 60 days, 30 by default.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18585,7 +18585,7 @@
       </c>
       <c r="E224" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F224" s="12" t="inlineStr">
@@ -18595,7 +18595,7 @@
       </c>
       <c r="G224" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI generates the Non-CBG request automatically after the client's confirmation, one per co-insurer; ours sends it when the user requests it.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18620,7 +18620,7 @@
       </c>
       <c r="E225" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F225" s="12" t="inlineStr">
@@ -18630,7 +18630,7 @@
       </c>
       <c r="G225" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: BDOI generates the Non-CBG request automatically after the client's confirmation, one per co-insurer; ours sends it when the user requests it.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18655,7 +18655,7 @@
       </c>
       <c r="E226" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F226" s="12" t="inlineStr">
@@ -18665,7 +18665,7 @@
       </c>
       <c r="G226" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Extension of 15 or 30 days from 7 days before the hold cover ends; ours allows a new request only after the previous hold cover expired or was cancelled.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18690,7 +18690,7 @@
       </c>
       <c r="E227" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F227" s="12" t="inlineStr">
@@ -18700,7 +18700,7 @@
       </c>
       <c r="G227" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Automatic CBG requests for Clean accounts 75 days before expiry, one Excel file per insurer.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18725,7 +18725,7 @@
       </c>
       <c r="E228" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F228" s="12" t="inlineStr">
@@ -18735,7 +18735,7 @@
       </c>
       <c r="G228" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Automatic 30-day extension for expired and unbooked CBG Home accounts on the 15th of each month.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18760,7 +18760,7 @@
       </c>
       <c r="E229" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F229" s="12" t="inlineStr">
@@ -18770,7 +18770,7 @@
       </c>
       <c r="G229" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours e-mails the request from the hold cover template; BDOI uploads to MFT for enrolled insurers and e-mails the others.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18795,7 +18795,7 @@
       </c>
       <c r="E230" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F230" s="12" t="inlineStr">
@@ -18805,7 +18805,7 @@
       </c>
       <c r="G230" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours records the confirmation by hand; BDOI also uploads response files (or MFT) matched on the reference number.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18830,7 +18830,7 @@
       </c>
       <c r="E231" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F231" s="12" t="inlineStr">
@@ -18840,7 +18840,7 @@
       </c>
       <c r="G231" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Approved and Rejected responses update the hold cover; a rejection returns the account to the user.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18865,7 +18865,7 @@
       </c>
       <c r="E232" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F232" s="12" t="inlineStr">
@@ -18875,7 +18875,7 @@
       </c>
       <c r="G232" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Approved and Rejected responses update the hold cover; a rejection returns the account to the user.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18900,7 +18900,7 @@
       </c>
       <c r="E233" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F233" s="12" t="inlineStr">
@@ -18910,7 +18910,7 @@
       </c>
       <c r="G233" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Summary of hold cover response files.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -18935,7 +18935,7 @@
       </c>
       <c r="E234" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F234" s="12" t="inlineStr">
@@ -18945,7 +18945,7 @@
       </c>
       <c r="G234" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: Record-level view of hold cover responses.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19005,7 +19005,7 @@
       </c>
       <c r="E236" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F236" s="12" t="inlineStr">
@@ -19015,7 +19015,7 @@
       </c>
       <c r="G236" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours keeps a list of non-renewable risk codes; BDOI keeps every risk code with a Renewable / Non-Renewable indicator, read-only to other users.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19040,7 +19040,7 @@
       </c>
       <c r="E237" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F237" s="12" t="inlineStr">
@@ -19050,7 +19050,7 @@
       </c>
       <c r="G237" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours keeps a list of non-renewable risk codes; BDOI keeps every risk code with a Renewable / Non-Renewable indicator, read-only to other users.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19075,7 +19075,7 @@
       </c>
       <c r="E238" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F238" s="12" t="inlineStr">
@@ -19085,7 +19085,7 @@
       </c>
       <c r="G238" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: View with description, line, indicator, status and the audit fields.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19110,7 +19110,7 @@
       </c>
       <c r="E239" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F239" s="12" t="inlineStr">
@@ -19120,7 +19120,7 @@
       </c>
       <c r="G239" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has effective-from and effective-to dates and a checker; BDOI blocks retroactive dates and duplicates with its messages and records the reason "Non-Renewable Risk Code" (ours "Non-renewable Accounts").</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19145,7 +19145,7 @@
       </c>
       <c r="E240" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F240" s="12" t="inlineStr">
@@ -19155,7 +19155,7 @@
       </c>
       <c r="G240" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has effective-from and effective-to dates and a checker; BDOI blocks retroactive dates and duplicates with its messages and records the reason "Non-Renewable Risk Code" (ours "Non-renewable Accounts").</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19180,7 +19180,7 @@
       </c>
       <c r="E241" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F241" s="12" t="inlineStr">
@@ -19190,7 +19190,7 @@
       </c>
       <c r="G241" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours has effective-from and effective-to dates and a checker; BDOI blocks retroactive dates and duplicates with its messages and records the reason "Non-Renewable Risk Code" (ours "Non-renewable Accounts").</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19215,7 +19215,7 @@
       </c>
       <c r="E242" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F242" s="12" t="inlineStr">
@@ -19225,7 +19225,7 @@
       </c>
       <c r="G242" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Update of a risk code with the same validations and log.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19250,7 +19250,7 @@
       </c>
       <c r="E243" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F243" s="12" t="inlineStr">
@@ -19260,7 +19260,7 @@
       </c>
       <c r="G243" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Update of a risk code with the same validations and log.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19285,7 +19285,7 @@
       </c>
       <c r="E244" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F244" s="12" t="inlineStr">
@@ -19295,7 +19295,7 @@
       </c>
       <c r="G244" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Both flag KYC due without blocking; BDOI makes the criteria configurable (schedules, expiry, bank / non-bank, product, regulation), ours reads the client's KYC review date.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19320,7 +19320,7 @@
       </c>
       <c r="E245" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F245" s="12" t="inlineStr">
@@ -19330,7 +19330,7 @@
       </c>
       <c r="G245" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: KYC statuses (Due, Upcoming, Not Required, Pending Follow-Up, Completed) with history and review activities.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19355,7 +19355,7 @@
       </c>
       <c r="E246" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F246" s="12" t="inlineStr">
@@ -19365,7 +19365,7 @@
       </c>
       <c r="G246" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: KYC monitoring dashboard with drill-down.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19495,7 +19495,7 @@
       </c>
       <c r="E250" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F250" s="12" t="inlineStr">
@@ -19505,7 +19505,7 @@
       </c>
       <c r="G250" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: BDOI keeps a list of RMU Account Officer codes and derives RMU from the AO code of the loan; ours takes RMU from the LAMD report.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19530,7 +19530,7 @@
       </c>
       <c r="E251" s="24" t="inlineStr">
         <is>
-          <t>No</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F251" s="12" t="inlineStr">
@@ -19540,7 +19540,7 @@
       </c>
       <c r="G251" s="12" t="inlineStr">
         <is>
-          <t>Planned for a later release: Comparison of BDOI's FRS with the system: BDOI keeps a list of RMU Account Officer codes and derives RMU from the AO code of the loan; ours takes RMU from the LAMD report.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19565,7 +19565,7 @@
       </c>
       <c r="E252" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F252" s="12" t="inlineStr">
@@ -19575,7 +19575,7 @@
       </c>
       <c r="G252" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Renewal annual budget maintenance; the system has production targets per sales unit in New Business.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19600,7 +19600,7 @@
       </c>
       <c r="E253" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F253" s="12" t="inlineStr">
@@ -19610,7 +19610,7 @@
       </c>
       <c r="G253" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Monthly new, renewal and organic budgets per unit, segment, region, team and officer with annual totals.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19635,7 +19635,7 @@
       </c>
       <c r="E254" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F254" s="12" t="inlineStr">
@@ -19645,7 +19645,7 @@
       </c>
       <c r="G254" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Budget upload with a template.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19670,7 +19670,7 @@
       </c>
       <c r="E255" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F255" s="12" t="inlineStr">
@@ -19680,7 +19680,7 @@
       </c>
       <c r="G255" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Budget validations (mandatory fiscal year and segment, region or team by segment, no negative values).</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19705,7 +19705,7 @@
       </c>
       <c r="E256" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F256" s="12" t="inlineStr">
@@ -19715,7 +19715,7 @@
       </c>
       <c r="G256" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Budget inquiry screen.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19740,7 +19740,7 @@
       </c>
       <c r="E257" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F257" s="12" t="inlineStr">
@@ -19750,7 +19750,7 @@
       </c>
       <c r="G257" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Budget history with previous and updated values.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19775,7 +19775,7 @@
       </c>
       <c r="E258" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F258" s="12" t="inlineStr">
@@ -19785,7 +19785,7 @@
       </c>
       <c r="G258" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours keeps an unchangeable history and audit per renewal with decision and sanitation reports; BDOI adds an Audit Logs menu with old and new values and export.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19810,7 +19810,7 @@
       </c>
       <c r="E259" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F259" s="12" t="inlineStr">
@@ -19820,7 +19820,7 @@
       </c>
       <c r="G259" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours keeps an unchangeable history and audit per renewal with decision and sanitation reports; BDOI adds an Audit Logs menu with old and new values and export.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19880,7 +19880,7 @@
       </c>
       <c r="E261" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F261" s="12" t="inlineStr">
@@ -19890,7 +19890,7 @@
       </c>
       <c r="G261" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours specifies the status report, the listing and six operational reports with their columns; BDOI lists 24 reports without layouts.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -19915,7 +19915,7 @@
       </c>
       <c r="E262" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F262" s="12" t="inlineStr">
@@ -19925,7 +19925,7 @@
       </c>
       <c r="G262" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Comparison of BDOI's FRS with the system: Ours specifies the status report, the listing and six operational reports with their columns; BDOI lists 24 reports without layouts.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -20020,7 +20020,7 @@
       </c>
       <c r="E265" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F265" s="12" t="inlineStr">
@@ -20030,7 +20030,7 @@
       </c>
       <c r="G265" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -20055,7 +20055,7 @@
       </c>
       <c r="E266" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F266" s="12" t="inlineStr">
@@ -20065,7 +20065,7 @@
       </c>
       <c r="G266" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -20090,7 +20090,7 @@
       </c>
       <c r="E267" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F267" s="12" t="inlineStr">
@@ -20100,7 +20100,7 @@
       </c>
       <c r="G267" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -20125,7 +20125,7 @@
       </c>
       <c r="E268" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F268" s="12" t="inlineStr">
@@ -20135,7 +20135,7 @@
       </c>
       <c r="G268" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -20160,7 +20160,7 @@
       </c>
       <c r="E269" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F269" s="12" t="inlineStr">
@@ -20170,7 +20170,7 @@
       </c>
       <c r="G269" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -20300,7 +20300,7 @@
       </c>
       <c r="E273" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F273" s="12" t="inlineStr">
@@ -20310,7 +20310,7 @@
       </c>
       <c r="G273" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -20335,7 +20335,7 @@
       </c>
       <c r="E274" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F274" s="12" t="inlineStr">
@@ -20345,7 +20345,7 @@
       </c>
       <c r="G274" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -20370,7 +20370,7 @@
       </c>
       <c r="E275" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F275" s="12" t="inlineStr">
@@ -20380,7 +20380,7 @@
       </c>
       <c r="G275" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -21140,7 +21140,7 @@
       </c>
       <c r="E297" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F297" s="12" t="inlineStr">
@@ -21150,7 +21150,7 @@
       </c>
       <c r="G297" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -21175,7 +21175,7 @@
       </c>
       <c r="E298" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F298" s="12" t="inlineStr">
@@ -21185,7 +21185,7 @@
       </c>
       <c r="G298" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -21210,7 +21210,7 @@
       </c>
       <c r="E299" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F299" s="12" t="inlineStr">
@@ -21220,7 +21220,7 @@
       </c>
       <c r="G299" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -21665,7 +21665,7 @@
       </c>
       <c r="E312" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F312" s="12" t="inlineStr">
@@ -21675,7 +21675,7 @@
       </c>
       <c r="G312" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -21700,7 +21700,7 @@
       </c>
       <c r="E313" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F313" s="12" t="inlineStr">
@@ -21710,7 +21710,7 @@
       </c>
       <c r="G313" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -21735,7 +21735,7 @@
       </c>
       <c r="E314" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F314" s="12" t="inlineStr">
@@ -21745,7 +21745,7 @@
       </c>
       <c r="G314" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -21770,7 +21770,7 @@
       </c>
       <c r="E315" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F315" s="12" t="inlineStr">
@@ -21780,7 +21780,7 @@
       </c>
       <c r="G315" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>
@@ -21805,7 +21805,7 @@
       </c>
       <c r="E316" s="24" t="inlineStr">
         <is>
-          <t>Partly</t>
+          <t>Yes</t>
         </is>
       </c>
       <c r="F316" s="12" t="inlineStr">
@@ -21815,7 +21815,7 @@
       </c>
       <c r="G316" s="12" t="inlineStr">
         <is>
-          <t>Partly available: Partly available: some acceptance criteria are partly conformant in the end-to-end run.</t>
+          <t>Available; confirmed with the acceptance test case in UAT.</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-06_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-06_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -746,7 +746,7 @@
       </c>
       <c r="C14" s="7" t="inlineStr">
         <is>
-          <t>10 October 2026</t>
+          <t>11 October 2026</t>
         </is>
       </c>
     </row>

--- a/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-06_FRS_Coverage_in_BIBS_v1.0.xlsx
+++ b/docs/deliverables/out/Programme/Quality/BIBS_Coverage_BRD-06_FRS_Coverage_in_BIBS_v1.0.xlsx
@@ -691,7 +691,7 @@
     <row r="8">
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>BRD-06 Renewal - FRS in BDOI's template v1.1 (internal)</t>
+          <t>BRD-06 Renewal - FRS in BDOI's template v1.2 (internal)</t>
         </is>
       </c>
     </row>
@@ -819,7 +819,7 @@
       </c>
       <c r="C21" s="14" t="inlineStr">
         <is>
-          <t>Coverage of the FRS v1.1 in the BIBS environment, by item count and by acceptance criterion</t>
+          <t>Coverage of the FRS v1.2 in the BIBS environment, by item count and by acceptance criterion</t>
         </is>
       </c>
       <c r="D21" s="14" t="n">
@@ -834,7 +834,7 @@
       </c>
       <c r="C22" s="12" t="inlineStr">
         <is>
-          <t>Every FR item and sub-item of the FRS v1.1</t>
+          <t>Every FR item and sub-item of the FRS v1.2</t>
         </is>
       </c>
       <c r="D22" s="12" t="n">
@@ -849,7 +849,7 @@
       </c>
       <c r="C23" s="14" t="inlineStr">
         <is>
-          <t>Every acceptance criterion of the FRS v1.1</t>
+          <t>Every acceptance criterion of the FRS v1.2</t>
         </is>
       </c>
       <c r="D23" s="14" t="n">
@@ -1433,7 +1433,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Coverage of the FRS v1.1 in the BIBS environment, by item count and by acceptance criterion</t>
+          <t>Coverage of the FRS v1.2 in the BIBS environment, by item count and by acceptance criterion</t>
         </is>
       </c>
     </row>
@@ -3722,7 +3722,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Every FR item and sub-item of the FRS v1.1</t>
+          <t>Every FR item and sub-item of the FRS v1.2</t>
         </is>
       </c>
     </row>
@@ -10849,7 +10849,7 @@
     <row r="2">
       <c r="A2" s="21" t="inlineStr">
         <is>
-          <t>Every acceptance criterion of the FRS v1.1</t>
+          <t>Every acceptance criterion of the FRS v1.2</t>
         </is>
       </c>
     </row>
